--- a/data/palacio_royal_09_12_2026.xlsx
+++ b/data/palacio_royal_09_12_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\renha\workspace\projects\big_boss_bro\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641DCCCA-D47E-4BE5-B19C-349DD65AE48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20DFF318-170E-4CE0-94C2-DAC8772A0FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="126">
   <si>
     <t>种类</t>
   </si>
@@ -91,16 +91,334 @@
   </si>
   <si>
     <t>Mediano/Grande</t>
+  </si>
+  <si>
+    <t>Arroz con puerco</t>
+  </si>
+  <si>
+    <t>Arroz blanco</t>
+  </si>
+  <si>
+    <t>Arroz con chorizo</t>
+  </si>
+  <si>
+    <t>Chow Mein</t>
+  </si>
+  <si>
+    <t>Chow mein cantones</t>
+  </si>
+  <si>
+    <t>Chow mein con pollo</t>
+  </si>
+  <si>
+    <t>Chow mein con res</t>
+  </si>
+  <si>
+    <t>Chow mein con camaron</t>
+  </si>
+  <si>
+    <t>He fen con res</t>
+  </si>
+  <si>
+    <t>He fen con camaron</t>
+  </si>
+  <si>
+    <t>He fen con pollo</t>
+  </si>
+  <si>
+    <t>He fen cantones</t>
+  </si>
+  <si>
+    <t>定制1选项价格</t>
+  </si>
+  <si>
+    <t>140/200</t>
+  </si>
+  <si>
+    <t>140/203</t>
+  </si>
+  <si>
+    <t>130/180</t>
+  </si>
+  <si>
+    <t>140/150</t>
+  </si>
+  <si>
+    <t>基础价格</t>
+  </si>
+  <si>
+    <t>185/240</t>
+  </si>
+  <si>
+    <t>160/220</t>
+  </si>
+  <si>
+    <t>180/240</t>
+  </si>
+  <si>
+    <t>140/185</t>
+  </si>
+  <si>
+    <t>175/250</t>
+  </si>
+  <si>
+    <t>150/200</t>
+  </si>
+  <si>
+    <t>Sizzling Hot Pot</t>
+  </si>
+  <si>
+    <t>Mariscos hot pot</t>
+  </si>
+  <si>
+    <t>Especial hot pot</t>
+  </si>
+  <si>
+    <t>Sizzling de camaron</t>
+  </si>
+  <si>
+    <t>Sizzling de pollo</t>
+  </si>
+  <si>
+    <t>Sizzling de res</t>
+  </si>
+  <si>
+    <t>Mariscos</t>
+  </si>
+  <si>
+    <t>Camaron con naranja</t>
+  </si>
+  <si>
+    <t>Camaron almendrado</t>
+  </si>
+  <si>
+    <t>Camaroncon brocoli</t>
+  </si>
+  <si>
+    <t>Camaron enchilado</t>
+  </si>
+  <si>
+    <t>Comninacion de masiscos</t>
+  </si>
+  <si>
+    <t>Calamar enchilado</t>
+  </si>
+  <si>
+    <t>200/310</t>
+  </si>
+  <si>
+    <t>200/300</t>
+  </si>
+  <si>
+    <t>Bebidas</t>
+  </si>
+  <si>
+    <t>Sodas</t>
+  </si>
+  <si>
+    <t>Te helado</t>
+  </si>
+  <si>
+    <t>Te caliente</t>
+  </si>
+  <si>
+    <t>Te caliente chino</t>
+  </si>
+  <si>
+    <t>Limonada</t>
+  </si>
+  <si>
+    <t>Limonada Mineral</t>
+  </si>
+  <si>
+    <t>Naranjada</t>
+  </si>
+  <si>
+    <t>Naranjada Mineral</t>
+  </si>
+  <si>
+    <t>Jugo de naranja</t>
+  </si>
+  <si>
+    <t>Café</t>
+  </si>
+  <si>
+    <t>Matcha Smoothie</t>
+  </si>
+  <si>
+    <t>Taro Smoothie</t>
+  </si>
+  <si>
+    <t>Chocolate Smoothie</t>
+  </si>
+  <si>
+    <t>Oreo Smoothie</t>
+  </si>
+  <si>
+    <t>Taro Boba</t>
+  </si>
+  <si>
+    <t>Matcha Boba</t>
+  </si>
+  <si>
+    <t>Jazmin Boba</t>
+  </si>
+  <si>
+    <t>Cerveza</t>
+  </si>
+  <si>
+    <t>Sapporo</t>
+  </si>
+  <si>
+    <t>Tsingtao</t>
+  </si>
+  <si>
+    <t>Clamato+Michelada</t>
+  </si>
+  <si>
+    <t>Paloma</t>
+  </si>
+  <si>
+    <t>JARRA</t>
+  </si>
+  <si>
+    <t>Yes/No</t>
+  </si>
+  <si>
+    <t>125/0</t>
+  </si>
+  <si>
+    <t>60/0</t>
+  </si>
+  <si>
+    <t>130/0</t>
+  </si>
+  <si>
+    <t>135/0</t>
+  </si>
+  <si>
+    <t>EXTRA BOBA</t>
+  </si>
+  <si>
+    <t>25/0</t>
+  </si>
+  <si>
+    <t>Tofu</t>
+  </si>
+  <si>
+    <t>Tofu de pollo</t>
+  </si>
+  <si>
+    <t>Tofu de res</t>
+  </si>
+  <si>
+    <t>Tofu de camaron</t>
+  </si>
+  <si>
+    <t>Tofu con verduras</t>
+  </si>
+  <si>
+    <t>Tofu kunpo</t>
+  </si>
+  <si>
+    <t>Botanas</t>
+  </si>
+  <si>
+    <t>Chun Kun</t>
+  </si>
+  <si>
+    <t>Chiles asados</t>
+  </si>
+  <si>
+    <t>Papas Fritas</t>
+  </si>
+  <si>
+    <t>Churritos</t>
+  </si>
+  <si>
+    <t>Queso wonto asado</t>
+  </si>
+  <si>
+    <t>Dumplings fritos / al vapor</t>
+  </si>
+  <si>
+    <t>Sesame balls</t>
+  </si>
+  <si>
+    <t>40/80</t>
+  </si>
+  <si>
+    <t>30/60</t>
+  </si>
+  <si>
+    <t>80/140</t>
+  </si>
+  <si>
+    <t>135/195</t>
+  </si>
+  <si>
+    <t>150/230</t>
+  </si>
+  <si>
+    <t>Caldos</t>
+  </si>
+  <si>
+    <t>Caldo wonton</t>
+  </si>
+  <si>
+    <t>Caldo de mariscos</t>
+  </si>
+  <si>
+    <t>Caldo de camaron</t>
+  </si>
+  <si>
+    <t>Caldo cantones</t>
+  </si>
+  <si>
+    <t>Caldo de alte</t>
+  </si>
+  <si>
+    <t>Clado mandarin</t>
+  </si>
+  <si>
+    <t>Caldo de pollo</t>
+  </si>
+  <si>
+    <t>Caldo de molleja</t>
+  </si>
+  <si>
+    <t>Caldo de verdura</t>
+  </si>
+  <si>
+    <t>Caldo con noodle solo per</t>
+  </si>
+  <si>
+    <t>Caldo con hefen chino solo por</t>
+  </si>
+  <si>
+    <t>165/250</t>
+  </si>
+  <si>
+    <t>155/230</t>
+  </si>
+  <si>
+    <t>120/180</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -408,16 +726,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="18.921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.921875" customWidth="1"/>
+    <col min="4" max="4" width="13.921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="13.921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -425,187 +745,1372 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>20</v>
+      <c r="C2">
+        <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
-        <v>20</v>
+      <c r="C3">
+        <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
-        <v>20</v>
+      <c r="C4">
+        <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
-        <v>20</v>
+      <c r="C5">
+        <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
-        <v>20</v>
+      <c r="C6">
+        <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="s">
-        <v>20</v>
+      <c r="C7">
+        <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
-        <v>20</v>
+      <c r="C8">
+        <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
-      <c r="C9" t="s">
-        <v>20</v>
+      <c r="C9">
+        <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
-      <c r="C10" t="s">
-        <v>20</v>
+      <c r="C10">
+        <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" t="s">
-        <v>20</v>
+      <c r="C11">
+        <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12" t="s">
         <v>18</v>
       </c>
-      <c r="C12" t="s">
-        <v>20</v>
+      <c r="C12">
+        <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
       </c>
-      <c r="C13" t="s">
-        <v>20</v>
+      <c r="C13">
+        <v>0</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" t="s">
+        <v>21</v>
+      </c>
+      <c r="F32" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" t="s">
+        <v>21</v>
+      </c>
+      <c r="F35" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37">
+        <v>45</v>
+      </c>
+      <c r="D37" t="s">
+        <v>84</v>
+      </c>
+      <c r="E37" t="s">
+        <v>85</v>
+      </c>
+      <c r="F37" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38">
+        <v>70</v>
+      </c>
+      <c r="D38" t="s">
+        <v>84</v>
+      </c>
+      <c r="E38" t="s">
+        <v>85</v>
+      </c>
+      <c r="F38" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39">
+        <v>90</v>
+      </c>
+      <c r="D39" t="s">
+        <v>84</v>
+      </c>
+      <c r="E39" t="s">
+        <v>85</v>
+      </c>
+      <c r="F39" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" t="s">
+        <v>66</v>
+      </c>
+      <c r="C40">
+        <v>50</v>
+      </c>
+      <c r="D40" t="s">
+        <v>84</v>
+      </c>
+      <c r="E40" t="s">
+        <v>85</v>
+      </c>
+      <c r="F40" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" t="s">
+        <v>67</v>
+      </c>
+      <c r="C41">
+        <v>65</v>
+      </c>
+      <c r="D41" t="s">
+        <v>84</v>
+      </c>
+      <c r="E41" t="s">
+        <v>85</v>
+      </c>
+      <c r="F41" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" t="s">
+        <v>68</v>
+      </c>
+      <c r="C42">
+        <v>50</v>
+      </c>
+      <c r="D42" t="s">
+        <v>84</v>
+      </c>
+      <c r="E42" t="s">
+        <v>85</v>
+      </c>
+      <c r="F42" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" t="s">
+        <v>69</v>
+      </c>
+      <c r="C43">
+        <v>65</v>
+      </c>
+      <c r="D43" t="s">
+        <v>84</v>
+      </c>
+      <c r="E43" t="s">
+        <v>85</v>
+      </c>
+      <c r="F43" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C45">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46" t="s">
+        <v>72</v>
+      </c>
+      <c r="C46">
+        <v>85</v>
+      </c>
+      <c r="D46" t="s">
+        <v>90</v>
+      </c>
+      <c r="E46" t="s">
+        <v>85</v>
+      </c>
+      <c r="F46" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" t="s">
+        <v>73</v>
+      </c>
+      <c r="C47">
+        <v>85</v>
+      </c>
+      <c r="D47" t="s">
+        <v>90</v>
+      </c>
+      <c r="E47" t="s">
+        <v>85</v>
+      </c>
+      <c r="F47" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" t="s">
+        <v>74</v>
+      </c>
+      <c r="C48">
+        <v>85</v>
+      </c>
+      <c r="D48" t="s">
+        <v>90</v>
+      </c>
+      <c r="E48" t="s">
+        <v>85</v>
+      </c>
+      <c r="F48" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" t="s">
+        <v>75</v>
+      </c>
+      <c r="C49">
+        <v>85</v>
+      </c>
+      <c r="D49" t="s">
+        <v>90</v>
+      </c>
+      <c r="E49" t="s">
+        <v>85</v>
+      </c>
+      <c r="F49" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50" t="s">
+        <v>76</v>
+      </c>
+      <c r="C50">
+        <v>88</v>
+      </c>
+      <c r="D50" t="s">
+        <v>90</v>
+      </c>
+      <c r="E50" t="s">
+        <v>85</v>
+      </c>
+      <c r="F50" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" t="s">
+        <v>77</v>
+      </c>
+      <c r="C51">
+        <v>88</v>
+      </c>
+      <c r="D51" t="s">
+        <v>90</v>
+      </c>
+      <c r="E51" t="s">
+        <v>85</v>
+      </c>
+      <c r="F51" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" t="s">
+        <v>78</v>
+      </c>
+      <c r="C52">
+        <v>88</v>
+      </c>
+      <c r="D52" t="s">
+        <v>90</v>
+      </c>
+      <c r="E52" t="s">
+        <v>85</v>
+      </c>
+      <c r="F52" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" t="s">
+        <v>79</v>
+      </c>
+      <c r="C53">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" t="s">
+        <v>80</v>
+      </c>
+      <c r="C54">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A55" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" t="s">
+        <v>81</v>
+      </c>
+      <c r="C55">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" t="s">
+        <v>82</v>
+      </c>
+      <c r="C56">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" t="s">
+        <v>83</v>
+      </c>
+      <c r="C57">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>92</v>
+      </c>
+      <c r="B58" t="s">
+        <v>93</v>
+      </c>
+      <c r="C58">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>92</v>
+      </c>
+      <c r="B59" t="s">
+        <v>94</v>
+      </c>
+      <c r="C59">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>92</v>
+      </c>
+      <c r="B60" t="s">
+        <v>95</v>
+      </c>
+      <c r="C60">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>92</v>
+      </c>
+      <c r="B61" t="s">
+        <v>96</v>
+      </c>
+      <c r="C61">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>92</v>
+      </c>
+      <c r="B62" t="s">
+        <v>97</v>
+      </c>
+      <c r="C62">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A63" t="s">
+        <v>98</v>
+      </c>
+      <c r="B63" t="s">
+        <v>99</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
+        <v>21</v>
+      </c>
+      <c r="F63" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>98</v>
+      </c>
+      <c r="B64" t="s">
+        <v>100</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64" t="s">
+        <v>20</v>
+      </c>
+      <c r="E64" t="s">
+        <v>21</v>
+      </c>
+      <c r="F64" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A65" t="s">
+        <v>98</v>
+      </c>
+      <c r="B65" t="s">
+        <v>101</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65" t="s">
+        <v>20</v>
+      </c>
+      <c r="E65" t="s">
+        <v>21</v>
+      </c>
+      <c r="F65" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A66" t="s">
+        <v>98</v>
+      </c>
+      <c r="B66" t="s">
+        <v>102</v>
+      </c>
+      <c r="C66">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A67" t="s">
+        <v>98</v>
+      </c>
+      <c r="B67" t="s">
+        <v>103</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" t="s">
+        <v>21</v>
+      </c>
+      <c r="F67" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A68" t="s">
+        <v>98</v>
+      </c>
+      <c r="B68" t="s">
+        <v>104</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68" t="s">
+        <v>20</v>
+      </c>
+      <c r="E68" t="s">
+        <v>21</v>
+      </c>
+      <c r="F68" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A69" t="s">
+        <v>98</v>
+      </c>
+      <c r="B69" t="s">
+        <v>105</v>
+      </c>
+      <c r="C69">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A70" t="s">
+        <v>111</v>
+      </c>
+      <c r="B70" t="s">
+        <v>112</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70" t="s">
+        <v>20</v>
+      </c>
+      <c r="E70" t="s">
+        <v>21</v>
+      </c>
+      <c r="F70" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A71" t="s">
+        <v>111</v>
+      </c>
+      <c r="B71" t="s">
+        <v>113</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71" t="s">
+        <v>20</v>
+      </c>
+      <c r="E71" t="s">
+        <v>21</v>
+      </c>
+      <c r="F71" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A72" t="s">
+        <v>111</v>
+      </c>
+      <c r="B72" t="s">
+        <v>114</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" t="s">
+        <v>21</v>
+      </c>
+      <c r="F72" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A73" t="s">
+        <v>111</v>
+      </c>
+      <c r="B73" t="s">
+        <v>115</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73" t="s">
+        <v>20</v>
+      </c>
+      <c r="E73" t="s">
+        <v>21</v>
+      </c>
+      <c r="F73" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A74" t="s">
+        <v>111</v>
+      </c>
+      <c r="B74" t="s">
+        <v>116</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E74" t="s">
+        <v>21</v>
+      </c>
+      <c r="F74" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A75" t="s">
+        <v>111</v>
+      </c>
+      <c r="B75" t="s">
+        <v>117</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75" t="s">
+        <v>20</v>
+      </c>
+      <c r="E75" t="s">
+        <v>21</v>
+      </c>
+      <c r="F75" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A76" t="s">
+        <v>111</v>
+      </c>
+      <c r="B76" t="s">
+        <v>118</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76" t="s">
+        <v>20</v>
+      </c>
+      <c r="E76" t="s">
+        <v>21</v>
+      </c>
+      <c r="F76" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A77" t="s">
+        <v>111</v>
+      </c>
+      <c r="B77" t="s">
+        <v>119</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77" t="s">
+        <v>20</v>
+      </c>
+      <c r="E77" t="s">
+        <v>21</v>
+      </c>
+      <c r="F77" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A78" t="s">
+        <v>111</v>
+      </c>
+      <c r="B78" t="s">
+        <v>120</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A79" t="s">
+        <v>111</v>
+      </c>
+      <c r="B79" t="s">
+        <v>121</v>
+      </c>
+      <c r="C79">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A80" t="s">
+        <v>111</v>
+      </c>
+      <c r="B80" t="s">
+        <v>122</v>
+      </c>
+      <c r="C80">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/palacio_royal_09_12_2026.xlsx
+++ b/data/palacio_royal_09_12_2026.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\renha\workspace\projects\big_boss_bro\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20DFF318-170E-4CE0-94C2-DAC8772A0FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB22764-848E-4355-A420-355ECA43809F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="206">
   <si>
     <t>种类</t>
   </si>
@@ -48,87 +59,18 @@
     <t>Vegetables</t>
   </si>
   <si>
-    <t>Verdura Cantones</t>
-  </si>
-  <si>
-    <t>Chop suey de pollo</t>
-  </si>
-  <si>
-    <t>Chop suey camaron</t>
-  </si>
-  <si>
-    <t>Chop suey de res</t>
-  </si>
-  <si>
-    <t>Chop suey de puerco</t>
-  </si>
-  <si>
-    <t>Chop suey de verdura</t>
-  </si>
-  <si>
-    <t>Chop suey especial</t>
-  </si>
-  <si>
     <t>Arroz</t>
   </si>
   <si>
-    <t>Arroz yangzhou</t>
-  </si>
-  <si>
-    <t>Arroz cantones</t>
-  </si>
-  <si>
-    <t>Arroz con camaron</t>
-  </si>
-  <si>
-    <t>Arroz con res</t>
-  </si>
-  <si>
-    <t>Arroz con pollo</t>
-  </si>
-  <si>
     <t>Size</t>
   </si>
   <si>
     <t>Mediano/Grande</t>
   </si>
   <si>
-    <t>Arroz con puerco</t>
-  </si>
-  <si>
-    <t>Arroz blanco</t>
-  </si>
-  <si>
-    <t>Arroz con chorizo</t>
-  </si>
-  <si>
     <t>Chow Mein</t>
   </si>
   <si>
-    <t>Chow mein cantones</t>
-  </si>
-  <si>
-    <t>Chow mein con pollo</t>
-  </si>
-  <si>
-    <t>Chow mein con res</t>
-  </si>
-  <si>
-    <t>Chow mein con camaron</t>
-  </si>
-  <si>
-    <t>He fen con res</t>
-  </si>
-  <si>
-    <t>He fen con camaron</t>
-  </si>
-  <si>
-    <t>He fen con pollo</t>
-  </si>
-  <si>
-    <t>He fen cantones</t>
-  </si>
-  <si>
     <t>定制1选项价格</t>
   </si>
   <si>
@@ -168,42 +110,9 @@
     <t>Sizzling Hot Pot</t>
   </si>
   <si>
-    <t>Mariscos hot pot</t>
-  </si>
-  <si>
-    <t>Especial hot pot</t>
-  </si>
-  <si>
-    <t>Sizzling de camaron</t>
-  </si>
-  <si>
-    <t>Sizzling de pollo</t>
-  </si>
-  <si>
-    <t>Sizzling de res</t>
-  </si>
-  <si>
     <t>Mariscos</t>
   </si>
   <si>
-    <t>Camaron con naranja</t>
-  </si>
-  <si>
-    <t>Camaron almendrado</t>
-  </si>
-  <si>
-    <t>Camaroncon brocoli</t>
-  </si>
-  <si>
-    <t>Camaron enchilado</t>
-  </si>
-  <si>
-    <t>Comninacion de masiscos</t>
-  </si>
-  <si>
-    <t>Calamar enchilado</t>
-  </si>
-  <si>
     <t>200/310</t>
   </si>
   <si>
@@ -213,138 +122,18 @@
     <t>Bebidas</t>
   </si>
   <si>
-    <t>Sodas</t>
-  </si>
-  <si>
-    <t>Te helado</t>
-  </si>
-  <si>
-    <t>Te caliente</t>
-  </si>
-  <si>
-    <t>Te caliente chino</t>
-  </si>
-  <si>
-    <t>Limonada</t>
-  </si>
-  <si>
-    <t>Limonada Mineral</t>
-  </si>
-  <si>
-    <t>Naranjada</t>
-  </si>
-  <si>
-    <t>Naranjada Mineral</t>
-  </si>
-  <si>
-    <t>Jugo de naranja</t>
-  </si>
-  <si>
-    <t>Café</t>
-  </si>
-  <si>
-    <t>Matcha Smoothie</t>
-  </si>
-  <si>
-    <t>Taro Smoothie</t>
-  </si>
-  <si>
-    <t>Chocolate Smoothie</t>
-  </si>
-  <si>
-    <t>Oreo Smoothie</t>
-  </si>
-  <si>
-    <t>Taro Boba</t>
-  </si>
-  <si>
-    <t>Matcha Boba</t>
-  </si>
-  <si>
-    <t>Jazmin Boba</t>
-  </si>
-  <si>
-    <t>Cerveza</t>
-  </si>
-  <si>
-    <t>Sapporo</t>
-  </si>
-  <si>
-    <t>Tsingtao</t>
-  </si>
-  <si>
-    <t>Clamato+Michelada</t>
-  </si>
-  <si>
-    <t>Paloma</t>
-  </si>
-  <si>
     <t>JARRA</t>
   </si>
   <si>
-    <t>Yes/No</t>
-  </si>
-  <si>
-    <t>125/0</t>
-  </si>
-  <si>
-    <t>60/0</t>
-  </si>
-  <si>
-    <t>130/0</t>
-  </si>
-  <si>
-    <t>135/0</t>
-  </si>
-  <si>
     <t>EXTRA BOBA</t>
   </si>
   <si>
-    <t>25/0</t>
-  </si>
-  <si>
     <t>Tofu</t>
   </si>
   <si>
-    <t>Tofu de pollo</t>
-  </si>
-  <si>
-    <t>Tofu de res</t>
-  </si>
-  <si>
-    <t>Tofu de camaron</t>
-  </si>
-  <si>
-    <t>Tofu con verduras</t>
-  </si>
-  <si>
-    <t>Tofu kunpo</t>
-  </si>
-  <si>
     <t>Botanas</t>
   </si>
   <si>
-    <t>Chun Kun</t>
-  </si>
-  <si>
-    <t>Chiles asados</t>
-  </si>
-  <si>
-    <t>Papas Fritas</t>
-  </si>
-  <si>
-    <t>Churritos</t>
-  </si>
-  <si>
-    <t>Queso wonto asado</t>
-  </si>
-  <si>
-    <t>Dumplings fritos / al vapor</t>
-  </si>
-  <si>
-    <t>Sesame balls</t>
-  </si>
-  <si>
     <t>40/80</t>
   </si>
   <si>
@@ -363,39 +152,6 @@
     <t>Caldos</t>
   </si>
   <si>
-    <t>Caldo wonton</t>
-  </si>
-  <si>
-    <t>Caldo de mariscos</t>
-  </si>
-  <si>
-    <t>Caldo de camaron</t>
-  </si>
-  <si>
-    <t>Caldo cantones</t>
-  </si>
-  <si>
-    <t>Caldo de alte</t>
-  </si>
-  <si>
-    <t>Clado mandarin</t>
-  </si>
-  <si>
-    <t>Caldo de pollo</t>
-  </si>
-  <si>
-    <t>Caldo de molleja</t>
-  </si>
-  <si>
-    <t>Caldo de verdura</t>
-  </si>
-  <si>
-    <t>Caldo con noodle solo per</t>
-  </si>
-  <si>
-    <t>Caldo con hefen chino solo por</t>
-  </si>
-  <si>
     <t>165/250</t>
   </si>
   <si>
@@ -403,6 +159,501 @@
   </si>
   <si>
     <t>120/180</t>
+  </si>
+  <si>
+    <t>Lonche</t>
+  </si>
+  <si>
+    <t>Cambio Arroz por Chow Mein cebollita</t>
+  </si>
+  <si>
+    <t>定制2选项价格</t>
+  </si>
+  <si>
+    <t>Cambio Arroz pollo por arriz con camaron</t>
+  </si>
+  <si>
+    <t>Postres</t>
+  </si>
+  <si>
+    <t>Carnes</t>
+  </si>
+  <si>
+    <t>195/290</t>
+  </si>
+  <si>
+    <t>155/200</t>
+  </si>
+  <si>
+    <t>Aves</t>
+  </si>
+  <si>
+    <t>Pollo</t>
+  </si>
+  <si>
+    <t>160/230</t>
+  </si>
+  <si>
+    <t>150/220</t>
+  </si>
+  <si>
+    <t>150/210</t>
+  </si>
+  <si>
+    <t>180/260</t>
+  </si>
+  <si>
+    <t>Paquete familiar</t>
+  </si>
+  <si>
+    <t>Especialidad</t>
+  </si>
+  <si>
+    <t>VERDURA CANTONES</t>
+  </si>
+  <si>
+    <t>CHOP SUEY DE POLLO</t>
+  </si>
+  <si>
+    <t>CHOP SUEY CAMARON</t>
+  </si>
+  <si>
+    <t>CHOP SUEY DE RES</t>
+  </si>
+  <si>
+    <t>CHOP SUEY DE PUERCO</t>
+  </si>
+  <si>
+    <t>CHOP SUEY DE VERDURA</t>
+  </si>
+  <si>
+    <t>CHOP SUEY ESPECIAL</t>
+  </si>
+  <si>
+    <t>ARROZ YANGZHOU</t>
+  </si>
+  <si>
+    <t>ARROZ CANTONES</t>
+  </si>
+  <si>
+    <t>ARROZ CON CAMARON</t>
+  </si>
+  <si>
+    <t>ARROZ CON RES</t>
+  </si>
+  <si>
+    <t>ARROZ CON POLLO</t>
+  </si>
+  <si>
+    <t>ARROZ CON PUERCO</t>
+  </si>
+  <si>
+    <t>ARROZ CON CHORIZO</t>
+  </si>
+  <si>
+    <t>ARROZ BLANCO</t>
+  </si>
+  <si>
+    <t>CHOW MEIN CANTONES</t>
+  </si>
+  <si>
+    <t>CHOW MEIN CON POLLO</t>
+  </si>
+  <si>
+    <t>CHOW MEIN CON RES</t>
+  </si>
+  <si>
+    <t>CHOW MEIN CON CAMARON</t>
+  </si>
+  <si>
+    <t>HE FEN CON RES</t>
+  </si>
+  <si>
+    <t>HE FEN CON CAMARON</t>
+  </si>
+  <si>
+    <t>HE FEN CON POLLO</t>
+  </si>
+  <si>
+    <t>HE FEN CANTONES</t>
+  </si>
+  <si>
+    <t>MARISCOS HOT POT</t>
+  </si>
+  <si>
+    <t>ESPECIAL HOT POT</t>
+  </si>
+  <si>
+    <t>SIZZLING DE CAMARON</t>
+  </si>
+  <si>
+    <t>SIZZLING DE POLLO</t>
+  </si>
+  <si>
+    <t>SIZZLING DE RES</t>
+  </si>
+  <si>
+    <t>CAMARON CON NARANJA</t>
+  </si>
+  <si>
+    <t>CAMARON ALMENDRADO</t>
+  </si>
+  <si>
+    <t>CAMARONCON BROCOLI</t>
+  </si>
+  <si>
+    <t>CAMARON ENCHILADO</t>
+  </si>
+  <si>
+    <t>COMNINACION DE MASISCOS</t>
+  </si>
+  <si>
+    <t>CALAMAR ENCHILADO</t>
+  </si>
+  <si>
+    <t>SODAS</t>
+  </si>
+  <si>
+    <t>TE HELADO</t>
+  </si>
+  <si>
+    <t>TE CALIENTE</t>
+  </si>
+  <si>
+    <t>TE CALIENTE CHINO</t>
+  </si>
+  <si>
+    <t>LIMONADA</t>
+  </si>
+  <si>
+    <t>LIMONADA MINERAL</t>
+  </si>
+  <si>
+    <t>NARANJADA</t>
+  </si>
+  <si>
+    <t>NARANJADA MINERAL</t>
+  </si>
+  <si>
+    <t>JUGO DE NARANJA</t>
+  </si>
+  <si>
+    <t>CAFÉ</t>
+  </si>
+  <si>
+    <t>MATCHA SMOOTHIE</t>
+  </si>
+  <si>
+    <t>TARO SMOOTHIE</t>
+  </si>
+  <si>
+    <t>CHOCOLATE SMOOTHIE</t>
+  </si>
+  <si>
+    <t>OREO SMOOTHIE</t>
+  </si>
+  <si>
+    <t>TARO BOBA</t>
+  </si>
+  <si>
+    <t>MATCHA BOBA</t>
+  </si>
+  <si>
+    <t>JAZMIN BOBA</t>
+  </si>
+  <si>
+    <t>CERVEZA</t>
+  </si>
+  <si>
+    <t>SAPPORO</t>
+  </si>
+  <si>
+    <t>TSINGTAO</t>
+  </si>
+  <si>
+    <t>CLAMATO+MICHELADA</t>
+  </si>
+  <si>
+    <t>PALOMA</t>
+  </si>
+  <si>
+    <t>TOFU DE POLLO</t>
+  </si>
+  <si>
+    <t>TOFU DE RES</t>
+  </si>
+  <si>
+    <t>TOFU DE CAMARON</t>
+  </si>
+  <si>
+    <t>TOFU CON VERDURAS</t>
+  </si>
+  <si>
+    <t>TOFU KUNPO</t>
+  </si>
+  <si>
+    <t>CHUN KUN</t>
+  </si>
+  <si>
+    <t>CHILES ASADOS</t>
+  </si>
+  <si>
+    <t>PAPAS FRITAS</t>
+  </si>
+  <si>
+    <t>CHURRITOS</t>
+  </si>
+  <si>
+    <t>QUESO WONTO ASADO</t>
+  </si>
+  <si>
+    <t>DUMPLINGS FRITOS / AL VAPOR</t>
+  </si>
+  <si>
+    <t>SESAME BALLS</t>
+  </si>
+  <si>
+    <t>CALDO WONTON</t>
+  </si>
+  <si>
+    <t>CALDO DE MARISCOS</t>
+  </si>
+  <si>
+    <t>CALDO DE CAMARON</t>
+  </si>
+  <si>
+    <t>CALDO CANTONES</t>
+  </si>
+  <si>
+    <t>CALDO DE ALTE</t>
+  </si>
+  <si>
+    <t>CLADO MANDARIN</t>
+  </si>
+  <si>
+    <t>CALDO DE POLLO</t>
+  </si>
+  <si>
+    <t>CALDO DE MOLLEJA</t>
+  </si>
+  <si>
+    <t>CALDO DE VERDURA</t>
+  </si>
+  <si>
+    <t>CALDO CON NOODLE SOLO PER</t>
+  </si>
+  <si>
+    <t>CALDO CON HEFEN CHINO SOLO POR</t>
+  </si>
+  <si>
+    <t>#1 CHOP SUEY DE POLLO</t>
+  </si>
+  <si>
+    <t>#2 POLLO CANTONES</t>
+  </si>
+  <si>
+    <t>#3 POLLO ASADO</t>
+  </si>
+  <si>
+    <t>#4 POLLO CON PINA</t>
+  </si>
+  <si>
+    <t>#5 POLLO ALMENDRADO</t>
+  </si>
+  <si>
+    <t>#6 POLLO ENCHILADO</t>
+  </si>
+  <si>
+    <t>#7 POLLO KUNG PAO</t>
+  </si>
+  <si>
+    <t>#8 POLLO MONGOLIA</t>
+  </si>
+  <si>
+    <t>#9 POLLO CON BROCOLI</t>
+  </si>
+  <si>
+    <t>#10 CHOW MEIN DE POLLO</t>
+  </si>
+  <si>
+    <t>#12 CARNITA DE PUERCO</t>
+  </si>
+  <si>
+    <t>#13 POLLO A LA NARANJA</t>
+  </si>
+  <si>
+    <t>#14 POLLO CON HONGO AL VAPOR</t>
+  </si>
+  <si>
+    <t>#15 RES CON BROCOLI</t>
+  </si>
+  <si>
+    <t>#16 PESCADO EMPANIZADO</t>
+  </si>
+  <si>
+    <t>#17 CHOP SUEY DE RES</t>
+  </si>
+  <si>
+    <t>#18 CHOW MEIN DE RES</t>
+  </si>
+  <si>
+    <t>#19 CHOP SUEY CON VERDURAS</t>
+  </si>
+  <si>
+    <t>#20 CAMARON CANTONES</t>
+  </si>
+  <si>
+    <t>#21 CHOP SUEY CAMARON</t>
+  </si>
+  <si>
+    <t>#22 CAMARON ALEMNDRADO</t>
+  </si>
+  <si>
+    <t>#23 CAMARON ENCHILADO</t>
+  </si>
+  <si>
+    <t>#24 CAMARON KUNG PAO</t>
+  </si>
+  <si>
+    <t>#25 CAMARON EMPANIZADO</t>
+  </si>
+  <si>
+    <t>#26 CHOW MEIN CON CAMARON</t>
+  </si>
+  <si>
+    <t>#27 COMBINACION CHINA</t>
+  </si>
+  <si>
+    <t>#28 COMBINACION MARISCOS</t>
+  </si>
+  <si>
+    <t>#29 CAMARON A LA NARANJA</t>
+  </si>
+  <si>
+    <t>#30 CALAMAR ENCHILADO</t>
+  </si>
+  <si>
+    <t>BBQ PORK BUN (3)</t>
+  </si>
+  <si>
+    <t>CUTE PIGGY (3)</t>
+  </si>
+  <si>
+    <t>MANTOU (6)</t>
+  </si>
+  <si>
+    <t>SESAME BALLS (8)</t>
+  </si>
+  <si>
+    <t>HAND CRAFTED ICE CREAM</t>
+  </si>
+  <si>
+    <t>ICE CREAM NIEVE</t>
+  </si>
+  <si>
+    <t>RES CON BROCOLI</t>
+  </si>
+  <si>
+    <t>RES MONGOLIA</t>
+  </si>
+  <si>
+    <t>CARNITAS DE PUERCO</t>
+  </si>
+  <si>
+    <t>CHORIZO CHINO</t>
+  </si>
+  <si>
+    <t>PATO EN SU JUGO</t>
+  </si>
+  <si>
+    <t>PATO CANTONES</t>
+  </si>
+  <si>
+    <t>PATO CON HONGOS</t>
+  </si>
+  <si>
+    <t>PERDIZ ASADA</t>
+  </si>
+  <si>
+    <t>PERDIZ ASADA CON HONGOS</t>
+  </si>
+  <si>
+    <t>DESHUESADO</t>
+  </si>
+  <si>
+    <t>POLLO CANTONES</t>
+  </si>
+  <si>
+    <t>POLLO MANDARIN</t>
+  </si>
+  <si>
+    <t>POLLO A LA NARANJA</t>
+  </si>
+  <si>
+    <t>POLLO CON BROCOLI</t>
+  </si>
+  <si>
+    <t>POLLO CON HONGOS AL VAPOR</t>
+  </si>
+  <si>
+    <t>POLLO CON PINA</t>
+  </si>
+  <si>
+    <t>POLLO CON COCO</t>
+  </si>
+  <si>
+    <t>POLLO ENCHILADO</t>
+  </si>
+  <si>
+    <t>POLLO MONGOLIA</t>
+  </si>
+  <si>
+    <t>POLLO ASADO</t>
+  </si>
+  <si>
+    <t>POLLO ASADO CON HONGOS</t>
+  </si>
+  <si>
+    <t>POLLO ALMENDRADO</t>
+  </si>
+  <si>
+    <t>POLLO KUNG PAO</t>
+  </si>
+  <si>
+    <t>POLLO CURRY</t>
+  </si>
+  <si>
+    <t>COMBINACION CHINA</t>
+  </si>
+  <si>
+    <t>NO.1</t>
+  </si>
+  <si>
+    <t>NO.2</t>
+  </si>
+  <si>
+    <t>NO.3</t>
+  </si>
+  <si>
+    <t>NO.4</t>
+  </si>
+  <si>
+    <t>NO.5</t>
+  </si>
+  <si>
+    <t>NO.6</t>
+  </si>
+  <si>
+    <t>MANDARIN ESPECIAL DE LA CASA</t>
+  </si>
+  <si>
+    <t>CAMARON CON MIEL Y NUEZ</t>
+  </si>
+  <si>
+    <t>ALITAS DE POLLO ENCHILADO</t>
+  </si>
+  <si>
+    <t>COMNINACION KUNG PAO</t>
   </si>
 </sst>
 </file>
@@ -444,8 +695,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -726,18 +980,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:I155"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="18.921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.921875" customWidth="1"/>
-    <col min="4" max="4" width="13.921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.921875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="13.921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -745,16 +1000,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -762,1351 +1017,2846 @@
       <c r="H1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>202</v>
       </c>
       <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+        <v>260</v>
+      </c>
+      <c r="D2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>203</v>
       </c>
       <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+        <v>330</v>
+      </c>
+      <c r="D3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>182</v>
       </c>
       <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+        <v>230</v>
+      </c>
+      <c r="D4"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>204</v>
       </c>
       <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+        <v>240</v>
+      </c>
+      <c r="D5"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>183</v>
       </c>
       <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+        <v>220</v>
+      </c>
+      <c r="D6"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>205</v>
       </c>
       <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+        <v>260</v>
+      </c>
+      <c r="D7"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>172</v>
       </c>
       <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+        <v>310</v>
+      </c>
+      <c r="D8"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>178</v>
       </c>
       <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+        <v>280</v>
+      </c>
+      <c r="D9"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+        <v>245</v>
+      </c>
+      <c r="D10"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>196</v>
       </c>
       <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+        <v>570</v>
+      </c>
+      <c r="D11"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+        <v>650</v>
+      </c>
+      <c r="D12"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>198</v>
       </c>
       <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+        <v>650</v>
+      </c>
+      <c r="D13"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>199</v>
       </c>
       <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+        <v>670</v>
+      </c>
+      <c r="D14"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>200</v>
       </c>
       <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+        <v>680</v>
+      </c>
+      <c r="D15"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>201</v>
       </c>
       <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" t="s">
-        <v>38</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="D16"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
-      <c r="D17" t="s">
-        <v>20</v>
+      <c r="D17" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18" t="s">
-        <v>20</v>
+        <v>182</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19" t="s">
-        <v>20</v>
+        <v>183</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20" t="s">
-        <v>20</v>
+        <v>184</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E20" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21">
-        <v>250</v>
+        <v>185</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22">
-        <v>250</v>
+        <v>186</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>187</v>
       </c>
       <c r="C23">
-        <v>230</v>
+        <v>240</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24">
-        <v>250</v>
+        <v>188</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>189</v>
       </c>
       <c r="C25">
-        <v>295</v>
+        <v>210</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26">
-        <v>295</v>
+        <v>190</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>49</v>
+        <v>191</v>
       </c>
       <c r="C27">
-        <v>295</v>
+        <v>250</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28">
-        <v>245</v>
+        <v>192</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29">
-        <v>295</v>
+        <v>193</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>194</v>
       </c>
       <c r="C30">
-        <v>0</v>
-      </c>
-      <c r="D30" t="s">
-        <v>20</v>
+        <v>230</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
+        <v>195</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
         <v>54</v>
-      </c>
-      <c r="C31">
-        <v>0</v>
-      </c>
-      <c r="D31" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>55</v>
+        <v>171</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
-      <c r="D32" t="s">
-        <v>20</v>
+      <c r="D32" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E32" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>172</v>
       </c>
       <c r="C33">
-        <v>0</v>
-      </c>
-      <c r="D33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" t="s">
-        <v>21</v>
-      </c>
-      <c r="F33" t="s">
-        <v>59</v>
+        <v>310</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>173</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
-      <c r="D34" t="s">
-        <v>20</v>
-      </c>
       <c r="E34" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>174</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
-      <c r="D35" t="s">
-        <v>20</v>
-      </c>
       <c r="E35" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B36" t="s">
-        <v>62</v>
+        <v>175</v>
       </c>
       <c r="C36">
-        <v>45</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="D36"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B37" t="s">
-        <v>63</v>
+        <v>176</v>
       </c>
       <c r="C37">
-        <v>45</v>
-      </c>
-      <c r="D37" t="s">
-        <v>84</v>
-      </c>
-      <c r="E37" t="s">
-        <v>85</v>
-      </c>
-      <c r="F37" t="s">
-        <v>86</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="D37"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>64</v>
+        <v>177</v>
       </c>
       <c r="C38">
-        <v>70</v>
-      </c>
-      <c r="D38" t="s">
-        <v>84</v>
-      </c>
-      <c r="E38" t="s">
-        <v>85</v>
-      </c>
-      <c r="F38" t="s">
-        <v>87</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="D38"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>65</v>
+        <v>178</v>
       </c>
       <c r="C39">
-        <v>90</v>
-      </c>
-      <c r="D39" t="s">
-        <v>84</v>
-      </c>
-      <c r="E39" t="s">
-        <v>85</v>
-      </c>
-      <c r="F39" t="s">
-        <v>87</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="D39"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>66</v>
+        <v>179</v>
       </c>
       <c r="C40">
-        <v>50</v>
-      </c>
-      <c r="D40" t="s">
-        <v>84</v>
-      </c>
-      <c r="E40" t="s">
-        <v>85</v>
-      </c>
-      <c r="F40" t="s">
-        <v>88</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="D40"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B41" t="s">
-        <v>67</v>
+        <v>180</v>
       </c>
       <c r="C41">
-        <v>65</v>
-      </c>
-      <c r="D41" t="s">
-        <v>84</v>
-      </c>
-      <c r="E41" t="s">
-        <v>85</v>
-      </c>
-      <c r="F41" t="s">
-        <v>89</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="D41"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C42">
-        <v>50</v>
-      </c>
-      <c r="D42" t="s">
-        <v>84</v>
+        <v>0</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E42" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="F42" t="s">
-        <v>88</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C43">
-        <v>65</v>
-      </c>
-      <c r="D43" t="s">
-        <v>84</v>
+        <v>0</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E43" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="F43" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C44">
-        <v>65</v>
+        <v>0</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C45">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C46">
-        <v>85</v>
-      </c>
-      <c r="D46" t="s">
-        <v>90</v>
+        <v>0</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E46" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="F46" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C47">
-        <v>85</v>
-      </c>
-      <c r="D47" t="s">
-        <v>90</v>
+        <v>0</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E47" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="F47" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C48">
-        <v>85</v>
-      </c>
-      <c r="D48" t="s">
-        <v>90</v>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E48" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="F48" t="s">
-        <v>91</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C49">
-        <v>85</v>
-      </c>
-      <c r="D49" t="s">
-        <v>90</v>
+        <v>0</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E49" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="F49" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="B50" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C50">
-        <v>88</v>
-      </c>
-      <c r="D50" t="s">
-        <v>90</v>
+        <v>0</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E50" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="F50" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="B51" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C51">
-        <v>88</v>
-      </c>
-      <c r="D51" t="s">
-        <v>90</v>
+        <v>0</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E51" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="F51" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="B52" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C52">
-        <v>88</v>
-      </c>
-      <c r="D52" t="s">
-        <v>90</v>
+        <v>0</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E52" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="F52" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="B53" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C53">
-        <v>65</v>
+        <v>0</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" t="s">
+        <v>9</v>
+      </c>
+      <c r="F53" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="B54" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C54">
-        <v>85</v>
+        <v>250</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="B55" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C55">
-        <v>95</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="B56" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C56">
-        <v>45</v>
+        <v>230</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="B57" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C57">
-        <v>150</v>
+        <v>250</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="B58" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="C58">
-        <v>240</v>
+        <v>0</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="B59" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="C59">
-        <v>290</v>
+        <v>0</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="B60" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="C60">
-        <v>290</v>
+        <v>0</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="B61" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="C61">
-        <v>240</v>
+        <v>35</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="B62" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="C62">
-        <v>240</v>
+        <v>0</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="B63" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
-      <c r="D63" t="s">
-        <v>20</v>
+      <c r="D63" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E63" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F63" t="s">
-        <v>106</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="B64" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="C64">
-        <v>0</v>
-      </c>
-      <c r="D64" t="s">
-        <v>20</v>
-      </c>
-      <c r="E64" t="s">
-        <v>21</v>
-      </c>
-      <c r="F64" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="B65" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
-      <c r="D65" t="s">
-        <v>20</v>
+      <c r="D65" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E65" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F65" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="B66" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="C66">
-        <v>35</v>
+        <v>0</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="B67" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
-      <c r="D67" t="s">
-        <v>20</v>
+      <c r="D67" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E67" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F67" t="s">
-        <v>109</v>
+        <v>39</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="B68" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
-      <c r="D68" t="s">
-        <v>20</v>
+      <c r="D68" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E68" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F68" t="s">
-        <v>110</v>
+        <v>39</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="B69" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="C69">
-        <v>140</v>
+        <v>0</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E69" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>111</v>
+        <v>37</v>
       </c>
       <c r="B70" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
-      <c r="D70" t="s">
-        <v>20</v>
+      <c r="D70" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E70" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F70" t="s">
-        <v>123</v>
+        <v>39</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>111</v>
+        <v>37</v>
       </c>
       <c r="B71" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
-      <c r="D71" t="s">
-        <v>20</v>
+      <c r="D71" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E71" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F71" t="s">
-        <v>124</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>111</v>
+        <v>37</v>
       </c>
       <c r="B72" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
-      <c r="D72" t="s">
-        <v>20</v>
+      <c r="D72" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E72" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F72" t="s">
-        <v>124</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>111</v>
+        <v>37</v>
       </c>
       <c r="B73" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
-      <c r="D73" t="s">
-        <v>20</v>
+      <c r="D73" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E73" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F73" t="s">
-        <v>124</v>
+        <v>40</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>111</v>
+        <v>37</v>
       </c>
       <c r="B74" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="C74">
-        <v>0</v>
-      </c>
-      <c r="D74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E74" t="s">
-        <v>21</v>
-      </c>
-      <c r="F74" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>111</v>
+        <v>37</v>
       </c>
       <c r="B75" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="C75">
-        <v>0</v>
-      </c>
-      <c r="D75" t="s">
-        <v>20</v>
-      </c>
-      <c r="E75" t="s">
-        <v>21</v>
-      </c>
-      <c r="F75" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="B76" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
-      <c r="D76" t="s">
-        <v>20</v>
+      <c r="D76" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E76" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F76" t="s">
-        <v>125</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="B77" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
-      <c r="D77" t="s">
-        <v>20</v>
+      <c r="D77" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E77" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F77" t="s">
-        <v>125</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="B78" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
-      <c r="D78" t="s">
-        <v>20</v>
+      <c r="D78" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E78" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F78" t="s">
-        <v>125</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="B79" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="C79">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E79" t="s">
+        <v>9</v>
+      </c>
+      <c r="F79" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
+        <v>24</v>
+      </c>
+      <c r="B80" t="s">
+        <v>89</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E80" t="s">
+        <v>9</v>
+      </c>
+      <c r="F80" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A81" t="s">
+        <v>24</v>
+      </c>
+      <c r="B81" t="s">
+        <v>90</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" t="s">
+        <v>9</v>
+      </c>
+      <c r="F81" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A82" t="s">
+        <v>6</v>
+      </c>
+      <c r="B82" t="s">
+        <v>57</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E82" t="s">
+        <v>9</v>
+      </c>
+      <c r="F82" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A83" t="s">
+        <v>6</v>
+      </c>
+      <c r="B83" t="s">
+        <v>58</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" t="s">
+        <v>9</v>
+      </c>
+      <c r="F83" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A84" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84" t="s">
+        <v>59</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E84" t="s">
+        <v>9</v>
+      </c>
+      <c r="F84" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A85" t="s">
+        <v>6</v>
+      </c>
+      <c r="B85" t="s">
+        <v>60</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E85" t="s">
+        <v>9</v>
+      </c>
+      <c r="F85" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A86" t="s">
+        <v>6</v>
+      </c>
+      <c r="B86" t="s">
+        <v>61</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E86" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A87" t="s">
+        <v>6</v>
+      </c>
+      <c r="B87" t="s">
+        <v>62</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E87" t="s">
+        <v>9</v>
+      </c>
+      <c r="F87" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A88" t="s">
+        <v>6</v>
+      </c>
+      <c r="B88" t="s">
+        <v>63</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E88" t="s">
+        <v>9</v>
+      </c>
+      <c r="F88" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A89" t="s">
+        <v>23</v>
+      </c>
+      <c r="B89" t="s">
+        <v>80</v>
+      </c>
+      <c r="C89">
+        <v>295</v>
+      </c>
+      <c r="D89"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A90" t="s">
+        <v>23</v>
+      </c>
+      <c r="B90" t="s">
+        <v>81</v>
+      </c>
+      <c r="C90">
+        <v>295</v>
+      </c>
+      <c r="D90"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A91" t="s">
+        <v>23</v>
+      </c>
+      <c r="B91" t="s">
+        <v>82</v>
+      </c>
+      <c r="C91">
+        <v>295</v>
+      </c>
+      <c r="D91"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A92" t="s">
+        <v>23</v>
+      </c>
+      <c r="B92" t="s">
+        <v>83</v>
+      </c>
+      <c r="C92">
+        <v>245</v>
+      </c>
+      <c r="D92"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A93" t="s">
+        <v>23</v>
+      </c>
+      <c r="B93" t="s">
+        <v>84</v>
+      </c>
+      <c r="C93">
+        <v>295</v>
+      </c>
+      <c r="D93"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A94" t="s">
+        <v>30</v>
+      </c>
+      <c r="B94" t="s">
+        <v>113</v>
+      </c>
+      <c r="C94">
+        <v>240</v>
+      </c>
+      <c r="D94"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A95" t="s">
+        <v>30</v>
+      </c>
+      <c r="B95" t="s">
+        <v>114</v>
+      </c>
+      <c r="C95">
+        <v>290</v>
+      </c>
+      <c r="D95"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A96" t="s">
+        <v>30</v>
+      </c>
+      <c r="B96" t="s">
+        <v>115</v>
+      </c>
+      <c r="C96">
+        <v>290</v>
+      </c>
+      <c r="D96"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A97" t="s">
+        <v>30</v>
+      </c>
+      <c r="B97" t="s">
+        <v>116</v>
+      </c>
+      <c r="C97">
+        <v>240</v>
+      </c>
+      <c r="D97"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A98" t="s">
+        <v>30</v>
+      </c>
+      <c r="B98" t="s">
+        <v>117</v>
+      </c>
+      <c r="C98">
+        <v>240</v>
+      </c>
+      <c r="D98"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A99" t="s">
+        <v>27</v>
+      </c>
+      <c r="B99" t="s">
+        <v>91</v>
+      </c>
+      <c r="C99">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A100" t="s">
+        <v>27</v>
+      </c>
+      <c r="B100" t="s">
+        <v>92</v>
+      </c>
+      <c r="C100">
+        <v>45</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F100">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A101" t="s">
+        <v>27</v>
+      </c>
+      <c r="B101" t="s">
+        <v>93</v>
+      </c>
+      <c r="C101">
+        <v>70</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F101">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A102" t="s">
+        <v>27</v>
+      </c>
+      <c r="B102" t="s">
+        <v>94</v>
+      </c>
+      <c r="C102">
+        <v>90</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F102">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A103" t="s">
+        <v>27</v>
+      </c>
+      <c r="B103" t="s">
+        <v>95</v>
+      </c>
+      <c r="C103">
+        <v>50</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F103">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A104" t="s">
+        <v>27</v>
+      </c>
+      <c r="B104" t="s">
+        <v>96</v>
+      </c>
+      <c r="C104">
+        <v>65</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F104">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
+        <v>27</v>
+      </c>
+      <c r="B105" t="s">
+        <v>97</v>
+      </c>
+      <c r="C105">
+        <v>50</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F105">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>27</v>
+      </c>
+      <c r="B106" t="s">
+        <v>98</v>
+      </c>
+      <c r="C106">
+        <v>65</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F106">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A107" t="s">
+        <v>27</v>
+      </c>
+      <c r="B107" t="s">
+        <v>99</v>
+      </c>
+      <c r="C107">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A108" t="s">
+        <v>27</v>
+      </c>
+      <c r="B108" t="s">
+        <v>100</v>
+      </c>
+      <c r="C108">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
+        <v>27</v>
+      </c>
+      <c r="B109" t="s">
+        <v>101</v>
+      </c>
+      <c r="C109">
+        <v>85</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F109">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A110" t="s">
+        <v>27</v>
+      </c>
+      <c r="B110" t="s">
+        <v>102</v>
+      </c>
+      <c r="C110">
+        <v>85</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F110">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A111" t="s">
+        <v>27</v>
+      </c>
+      <c r="B111" t="s">
+        <v>103</v>
+      </c>
+      <c r="C111">
+        <v>85</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F111">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A112" t="s">
+        <v>27</v>
+      </c>
+      <c r="B112" t="s">
+        <v>104</v>
+      </c>
+      <c r="C112">
+        <v>85</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F112">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A113" t="s">
+        <v>27</v>
+      </c>
+      <c r="B113" t="s">
+        <v>105</v>
+      </c>
+      <c r="C113">
+        <v>88</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F113">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A114" t="s">
+        <v>27</v>
+      </c>
+      <c r="B114" t="s">
+        <v>106</v>
+      </c>
+      <c r="C114">
+        <v>88</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F114">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A115" t="s">
+        <v>27</v>
+      </c>
+      <c r="B115" t="s">
+        <v>107</v>
+      </c>
+      <c r="C115">
+        <v>88</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F115">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A116" t="s">
+        <v>27</v>
+      </c>
+      <c r="B116" t="s">
+        <v>108</v>
+      </c>
+      <c r="C116">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A117" t="s">
+        <v>27</v>
+      </c>
+      <c r="B117" t="s">
+        <v>109</v>
+      </c>
+      <c r="C117">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A118" t="s">
+        <v>27</v>
+      </c>
+      <c r="B118" t="s">
+        <v>110</v>
+      </c>
+      <c r="C118">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A119" t="s">
+        <v>27</v>
+      </c>
+      <c r="B119" t="s">
         <v>111</v>
       </c>
-      <c r="B80" t="s">
-        <v>122</v>
-      </c>
-      <c r="C80">
-        <v>70</v>
+      <c r="C119">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A120" t="s">
+        <v>27</v>
+      </c>
+      <c r="B120" t="s">
+        <v>112</v>
+      </c>
+      <c r="C120">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A121" t="s">
+        <v>41</v>
+      </c>
+      <c r="B121" t="s">
+        <v>136</v>
+      </c>
+      <c r="C121">
+        <v>160</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F121">
+        <v>70</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I121">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A122" t="s">
+        <v>41</v>
+      </c>
+      <c r="B122" t="s">
+        <v>137</v>
+      </c>
+      <c r="C122">
+        <v>160</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F122">
+        <v>70</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I122">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A123" t="s">
+        <v>41</v>
+      </c>
+      <c r="B123" t="s">
+        <v>138</v>
+      </c>
+      <c r="C123">
+        <v>175</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F123">
+        <v>70</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I123">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A124" t="s">
+        <v>41</v>
+      </c>
+      <c r="B124" t="s">
+        <v>139</v>
+      </c>
+      <c r="C124">
+        <v>180</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F124">
+        <v>70</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I124">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A125" t="s">
+        <v>41</v>
+      </c>
+      <c r="B125" t="s">
+        <v>140</v>
+      </c>
+      <c r="C125">
+        <v>165</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F125">
+        <v>70</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I125">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A126" t="s">
+        <v>41</v>
+      </c>
+      <c r="B126" t="s">
+        <v>141</v>
+      </c>
+      <c r="C126">
+        <v>180</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F126">
+        <v>70</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I126">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A127" t="s">
+        <v>41</v>
+      </c>
+      <c r="B127" t="s">
+        <v>142</v>
+      </c>
+      <c r="C127">
+        <v>175</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F127">
+        <v>70</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I127">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A128" t="s">
+        <v>41</v>
+      </c>
+      <c r="B128" t="s">
+        <v>143</v>
+      </c>
+      <c r="C128">
+        <v>175</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F128">
+        <v>70</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I128">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A129" t="s">
+        <v>41</v>
+      </c>
+      <c r="B129" t="s">
+        <v>144</v>
+      </c>
+      <c r="C129">
+        <v>160</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F129">
+        <v>70</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I129">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A130" t="s">
+        <v>41</v>
+      </c>
+      <c r="B130" t="s">
+        <v>145</v>
+      </c>
+      <c r="C130">
+        <v>180</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F130">
+        <v>70</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I130">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A131" t="s">
+        <v>41</v>
+      </c>
+      <c r="B131" t="s">
+        <v>146</v>
+      </c>
+      <c r="C131">
+        <v>180</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F131">
+        <v>70</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I131">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A132" t="s">
+        <v>41</v>
+      </c>
+      <c r="B132" t="s">
+        <v>147</v>
+      </c>
+      <c r="C132">
+        <v>180</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F132">
+        <v>70</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I132">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A133" t="s">
+        <v>41</v>
+      </c>
+      <c r="B133" t="s">
+        <v>148</v>
+      </c>
+      <c r="C133">
+        <v>175</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F133">
+        <v>70</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I133">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A134" t="s">
+        <v>41</v>
+      </c>
+      <c r="B134" t="s">
+        <v>149</v>
+      </c>
+      <c r="C134">
+        <v>210</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F134">
+        <v>70</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I134">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A135" t="s">
+        <v>41</v>
+      </c>
+      <c r="B135" t="s">
+        <v>150</v>
+      </c>
+      <c r="C135">
+        <v>180</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F135">
+        <v>70</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I135">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A136" t="s">
+        <v>41</v>
+      </c>
+      <c r="B136" t="s">
+        <v>151</v>
+      </c>
+      <c r="C136">
+        <v>210</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F136">
+        <v>70</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I136">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A137" t="s">
+        <v>41</v>
+      </c>
+      <c r="B137" t="s">
+        <v>152</v>
+      </c>
+      <c r="C137">
+        <v>210</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F137">
+        <v>70</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I137">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A138" t="s">
+        <v>41</v>
+      </c>
+      <c r="B138" t="s">
+        <v>153</v>
+      </c>
+      <c r="C138">
+        <v>160</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F138">
+        <v>70</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I138">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A139" t="s">
+        <v>41</v>
+      </c>
+      <c r="B139" t="s">
+        <v>154</v>
+      </c>
+      <c r="C139">
+        <v>225</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F139">
+        <v>70</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I139">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A140" t="s">
+        <v>41</v>
+      </c>
+      <c r="B140" t="s">
+        <v>155</v>
+      </c>
+      <c r="C140">
+        <v>225</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F140">
+        <v>70</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I140">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A141" t="s">
+        <v>41</v>
+      </c>
+      <c r="B141" t="s">
+        <v>156</v>
+      </c>
+      <c r="C141">
+        <v>225</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F141">
+        <v>70</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I141">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A142" t="s">
+        <v>41</v>
+      </c>
+      <c r="B142" t="s">
+        <v>157</v>
+      </c>
+      <c r="C142">
+        <v>225</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F142">
+        <v>70</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I142">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A143" t="s">
+        <v>41</v>
+      </c>
+      <c r="B143" t="s">
+        <v>158</v>
+      </c>
+      <c r="C143">
+        <v>225</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F143">
+        <v>70</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I143">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A144" t="s">
+        <v>41</v>
+      </c>
+      <c r="B144" t="s">
+        <v>159</v>
+      </c>
+      <c r="C144">
+        <v>225</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F144">
+        <v>70</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I144">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A145" t="s">
+        <v>41</v>
+      </c>
+      <c r="B145" t="s">
+        <v>160</v>
+      </c>
+      <c r="C145">
+        <v>215</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F145">
+        <v>70</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I145">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A146" t="s">
+        <v>41</v>
+      </c>
+      <c r="B146" t="s">
+        <v>161</v>
+      </c>
+      <c r="C146">
+        <v>220</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F146">
+        <v>70</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H146" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I146">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A147" t="s">
+        <v>41</v>
+      </c>
+      <c r="B147" t="s">
+        <v>162</v>
+      </c>
+      <c r="C147">
+        <v>225</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F147">
+        <v>70</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I147">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A148" t="s">
+        <v>41</v>
+      </c>
+      <c r="B148" t="s">
+        <v>163</v>
+      </c>
+      <c r="C148">
+        <v>225</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F148">
+        <v>70</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I148">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A149" t="s">
+        <v>41</v>
+      </c>
+      <c r="B149" t="s">
+        <v>164</v>
+      </c>
+      <c r="C149">
+        <v>225</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F149">
+        <v>70</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I149">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A150" t="s">
+        <v>45</v>
+      </c>
+      <c r="B150" t="s">
+        <v>165</v>
+      </c>
+      <c r="C150">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A151" t="s">
+        <v>45</v>
+      </c>
+      <c r="B151" t="s">
+        <v>166</v>
+      </c>
+      <c r="C151">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A152" t="s">
+        <v>45</v>
+      </c>
+      <c r="B152" t="s">
+        <v>167</v>
+      </c>
+      <c r="C152">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A153" t="s">
+        <v>45</v>
+      </c>
+      <c r="B153" t="s">
+        <v>168</v>
+      </c>
+      <c r="C153">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A154" t="s">
+        <v>45</v>
+      </c>
+      <c r="B154" t="s">
+        <v>169</v>
+      </c>
+      <c r="C154">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A155" t="s">
+        <v>45</v>
+      </c>
+      <c r="B155" t="s">
+        <v>170</v>
+      </c>
+      <c r="C155">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/data/palacio_royal_09_12_2026.xlsx
+++ b/data/palacio_royal_09_12_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\renha\workspace\projects\big_boss_bro\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A43AB5D9-1837-4A46-B9D8-EB4CD4100BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42221D6B-1F3D-4982-9A47-90F5958DA723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="293">
   <si>
     <t>种类</t>
   </si>
@@ -149,9 +150,6 @@
     <t>Pollo Mandarin</t>
   </si>
   <si>
-    <t>Comninacion Kung Pao</t>
-  </si>
-  <si>
     <t>Res Mongolia</t>
   </si>
   <si>
@@ -335,9 +333,6 @@
     <t>Camaron Enchilado</t>
   </si>
   <si>
-    <t>Comninacion De Masiscos</t>
-  </si>
-  <si>
     <t>Calamar Enchilado</t>
   </si>
   <si>
@@ -545,12 +540,6 @@
     <t>POSTRES</t>
   </si>
   <si>
-    <t>Cambio Arroz por Chow Mein Cebollita</t>
-  </si>
-  <si>
-    <t>Cambio Arroz Pollo por Arroz con Camaron</t>
-  </si>
-  <si>
     <t>Chico/Mediano/Grande</t>
   </si>
   <si>
@@ -656,93 +645,6 @@
     <t>Lonche #30 Calamar enchilado</t>
   </si>
   <si>
-    <t>L #1</t>
-  </si>
-  <si>
-    <t>L #2</t>
-  </si>
-  <si>
-    <t>L #3</t>
-  </si>
-  <si>
-    <t>L #4</t>
-  </si>
-  <si>
-    <t>L #5</t>
-  </si>
-  <si>
-    <t>L #6</t>
-  </si>
-  <si>
-    <t>L #7</t>
-  </si>
-  <si>
-    <t>L #8</t>
-  </si>
-  <si>
-    <t>L #9</t>
-  </si>
-  <si>
-    <t>L #10</t>
-  </si>
-  <si>
-    <t>L #12</t>
-  </si>
-  <si>
-    <t>L #13</t>
-  </si>
-  <si>
-    <t>L #14</t>
-  </si>
-  <si>
-    <t>L #15</t>
-  </si>
-  <si>
-    <t>L #16</t>
-  </si>
-  <si>
-    <t>L #17</t>
-  </si>
-  <si>
-    <t>L #18</t>
-  </si>
-  <si>
-    <t>L #19</t>
-  </si>
-  <si>
-    <t>L #20</t>
-  </si>
-  <si>
-    <t>L #21</t>
-  </si>
-  <si>
-    <t>L #22</t>
-  </si>
-  <si>
-    <t>L #23</t>
-  </si>
-  <si>
-    <t>L #24</t>
-  </si>
-  <si>
-    <t>L #25</t>
-  </si>
-  <si>
-    <t>L #26</t>
-  </si>
-  <si>
-    <t>L #27</t>
-  </si>
-  <si>
-    <t>L #28</t>
-  </si>
-  <si>
-    <t>L #29</t>
-  </si>
-  <si>
-    <t>L #30</t>
-  </si>
-  <si>
     <t>Pollo Naranja</t>
   </si>
   <si>
@@ -803,9 +705,6 @@
     <t>Camaron Naranja</t>
   </si>
   <si>
-    <t>Comninacio Masiscos</t>
-  </si>
-  <si>
     <t>Arroz Camaron</t>
   </si>
   <si>
@@ -821,12 +720,6 @@
     <t>Arroz Chorizo</t>
   </si>
   <si>
-    <t>con Noodle</t>
-  </si>
-  <si>
-    <t>con Hefen</t>
-  </si>
-  <si>
     <t>Chow Mein Pollo</t>
   </si>
   <si>
@@ -876,6 +769,153 @@
   </si>
   <si>
     <t>定制3选项价格</t>
+  </si>
+  <si>
+    <t>Pollo A La Plancha</t>
+  </si>
+  <si>
+    <t>Pollo Plancha</t>
+  </si>
+  <si>
+    <t>Combinacion Kung Pao</t>
+  </si>
+  <si>
+    <t>Combinacion De Mariscos</t>
+  </si>
+  <si>
+    <t>Combinacion Mariscos</t>
+  </si>
+  <si>
+    <t>L#1</t>
+  </si>
+  <si>
+    <t>L#2</t>
+  </si>
+  <si>
+    <t>L#3</t>
+  </si>
+  <si>
+    <t>L#4</t>
+  </si>
+  <si>
+    <t>L#5</t>
+  </si>
+  <si>
+    <t>L#6</t>
+  </si>
+  <si>
+    <t>L#7</t>
+  </si>
+  <si>
+    <t>L#8</t>
+  </si>
+  <si>
+    <t>L#9</t>
+  </si>
+  <si>
+    <t>L#10</t>
+  </si>
+  <si>
+    <t>L#12</t>
+  </si>
+  <si>
+    <t>L#13</t>
+  </si>
+  <si>
+    <t>L#14</t>
+  </si>
+  <si>
+    <t>L#15</t>
+  </si>
+  <si>
+    <t>L#16</t>
+  </si>
+  <si>
+    <t>L#17</t>
+  </si>
+  <si>
+    <t>L#18</t>
+  </si>
+  <si>
+    <t>L#19</t>
+  </si>
+  <si>
+    <t>L#20</t>
+  </si>
+  <si>
+    <t>L#21</t>
+  </si>
+  <si>
+    <t>L#22</t>
+  </si>
+  <si>
+    <t>L#23</t>
+  </si>
+  <si>
+    <t>L#24</t>
+  </si>
+  <si>
+    <t>L#25</t>
+  </si>
+  <si>
+    <t>L#26</t>
+  </si>
+  <si>
+    <t>L#27</t>
+  </si>
+  <si>
+    <t>L#28</t>
+  </si>
+  <si>
+    <t>L#29</t>
+  </si>
+  <si>
+    <t>L#30</t>
+  </si>
+  <si>
+    <t>Lonche Chow Mein Verduras</t>
+  </si>
+  <si>
+    <t>L# Chow Mein Verduras</t>
+  </si>
+  <si>
+    <t>VASO/MEDIA JARRA/JARRA</t>
+  </si>
+  <si>
+    <t>45/130/170</t>
+  </si>
+  <si>
+    <t>Topo Chico</t>
+  </si>
+  <si>
+    <t>Botella Agua</t>
+  </si>
+  <si>
+    <t>90/120/150</t>
+  </si>
+  <si>
+    <t>Sriracha</t>
+  </si>
+  <si>
+    <t>Soda Especial</t>
+  </si>
+  <si>
+    <t>Mochi</t>
+  </si>
+  <si>
+    <t>Boba Latte</t>
+  </si>
+  <si>
+    <t>Te Caliente Pac</t>
+  </si>
+  <si>
+    <t>Galleta</t>
+  </si>
+  <si>
+    <t>Ciruela</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -1202,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T158"/>
+  <dimension ref="A1:T166"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="27.3046875" bestFit="1" customWidth="1"/>
@@ -1225,13 +1265,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D1" t="s">
         <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>2</v>
@@ -1252,24 +1292,24 @@
         <v>29</v>
       </c>
       <c r="L1" t="s">
-        <v>277</v>
+        <v>241</v>
       </c>
       <c r="M1" t="s">
-        <v>278</v>
+        <v>242</v>
       </c>
       <c r="N1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="72.900000000000006" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C2" t="s">
-        <v>206</v>
+        <v>249</v>
       </c>
       <c r="D2">
         <v>160</v>
@@ -1277,34 +1317,17 @@
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H2">
-        <v>70</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J2"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C3" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
       <c r="D3">
         <v>160</v>
@@ -1312,34 +1335,17 @@
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H3">
-        <v>70</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J3"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C4" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
       <c r="D4">
         <v>175</v>
@@ -1347,34 +1353,17 @@
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H4">
-        <v>70</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K4">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J4"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B5" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C5" t="s">
-        <v>209</v>
+        <v>252</v>
       </c>
       <c r="D5">
         <v>180</v>
@@ -1382,34 +1371,17 @@
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H5">
-        <v>70</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K5">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J5"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C6" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="D6">
         <v>165</v>
@@ -1417,34 +1389,17 @@
       <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H6">
-        <v>70</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K6">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J6"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B7" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C7" t="s">
-        <v>211</v>
+        <v>254</v>
       </c>
       <c r="D7">
         <v>180</v>
@@ -1452,34 +1407,17 @@
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H7">
-        <v>70</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K7">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J7"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B8" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C8" t="s">
-        <v>212</v>
+        <v>255</v>
       </c>
       <c r="D8">
         <v>175</v>
@@ -1487,34 +1425,17 @@
       <c r="E8">
         <v>1</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H8">
-        <v>70</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K8">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J8"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B9" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C9" t="s">
-        <v>213</v>
+        <v>256</v>
       </c>
       <c r="D9">
         <v>175</v>
@@ -1522,34 +1443,17 @@
       <c r="E9">
         <v>1</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H9">
-        <v>70</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K9">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J9"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C10" t="s">
-        <v>214</v>
+        <v>257</v>
       </c>
       <c r="D10">
         <v>160</v>
@@ -1557,34 +1461,17 @@
       <c r="E10">
         <v>1</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H10">
-        <v>70</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K10">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J10"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B11" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C11" t="s">
-        <v>215</v>
+        <v>258</v>
       </c>
       <c r="D11">
         <v>180</v>
@@ -1592,34 +1479,17 @@
       <c r="E11">
         <v>1</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H11">
-        <v>70</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K11">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J11"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B12" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C12" t="s">
-        <v>216</v>
+        <v>259</v>
       </c>
       <c r="D12">
         <v>180</v>
@@ -1627,34 +1497,17 @@
       <c r="E12">
         <v>1</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H12">
-        <v>70</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K12">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J12"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C13" t="s">
-        <v>217</v>
+        <v>260</v>
       </c>
       <c r="D13">
         <v>180</v>
@@ -1662,34 +1515,17 @@
       <c r="E13">
         <v>1</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H13">
-        <v>70</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K13">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J13"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C14" t="s">
-        <v>218</v>
+        <v>261</v>
       </c>
       <c r="D14">
         <v>175</v>
@@ -1697,34 +1533,17 @@
       <c r="E14">
         <v>1</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H14">
-        <v>70</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K14">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J14"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C15" t="s">
-        <v>219</v>
+        <v>262</v>
       </c>
       <c r="D15">
         <v>210</v>
@@ -1732,34 +1551,17 @@
       <c r="E15">
         <v>1</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H15">
-        <v>70</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K15">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J15"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B16" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C16" t="s">
-        <v>220</v>
+        <v>263</v>
       </c>
       <c r="D16">
         <v>180</v>
@@ -1767,34 +1569,17 @@
       <c r="E16">
         <v>1</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H16">
-        <v>70</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K16">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J16"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B17" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C17" t="s">
-        <v>221</v>
+        <v>264</v>
       </c>
       <c r="D17">
         <v>210</v>
@@ -1802,34 +1587,17 @@
       <c r="E17">
         <v>1</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H17">
-        <v>70</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K17">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J17"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B18" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C18" t="s">
-        <v>222</v>
+        <v>265</v>
       </c>
       <c r="D18">
         <v>210</v>
@@ -1837,34 +1605,17 @@
       <c r="E18">
         <v>1</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H18">
-        <v>70</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K18">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J18"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B19" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C19" t="s">
-        <v>223</v>
+        <v>266</v>
       </c>
       <c r="D19">
         <v>160</v>
@@ -1872,34 +1623,17 @@
       <c r="E19">
         <v>1</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H19">
-        <v>70</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K19">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J19"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B20" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C20" t="s">
-        <v>224</v>
+        <v>267</v>
       </c>
       <c r="D20">
         <v>225</v>
@@ -1907,34 +1641,17 @@
       <c r="E20">
         <v>1</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H20">
-        <v>70</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K20">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J20"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B21" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C21" t="s">
-        <v>225</v>
+        <v>268</v>
       </c>
       <c r="D21">
         <v>225</v>
@@ -1942,34 +1659,17 @@
       <c r="E21">
         <v>1</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H21">
-        <v>70</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K21">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J21"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B22" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C22" t="s">
-        <v>226</v>
+        <v>269</v>
       </c>
       <c r="D22">
         <v>225</v>
@@ -1977,34 +1677,17 @@
       <c r="E22">
         <v>1</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H22">
-        <v>70</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K22">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J22"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B23" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C23" t="s">
-        <v>227</v>
+        <v>270</v>
       </c>
       <c r="D23">
         <v>225</v>
@@ -2012,34 +1695,17 @@
       <c r="E23">
         <v>1</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H23">
-        <v>70</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K23">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J23"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B24" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C24" t="s">
-        <v>228</v>
+        <v>271</v>
       </c>
       <c r="D24">
         <v>225</v>
@@ -2047,34 +1713,17 @@
       <c r="E24">
         <v>1</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H24">
-        <v>70</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K24">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J24"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B25" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C25" t="s">
-        <v>229</v>
+        <v>272</v>
       </c>
       <c r="D25">
         <v>225</v>
@@ -2082,34 +1731,17 @@
       <c r="E25">
         <v>1</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H25">
-        <v>70</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K25">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J25"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B26" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C26" t="s">
-        <v>230</v>
+        <v>273</v>
       </c>
       <c r="D26">
         <v>215</v>
@@ -2117,34 +1749,17 @@
       <c r="E26">
         <v>1</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H26">
-        <v>70</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K26">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J26"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B27" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C27" t="s">
-        <v>231</v>
+        <v>274</v>
       </c>
       <c r="D27">
         <v>220</v>
@@ -2152,34 +1767,17 @@
       <c r="E27">
         <v>1</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H27">
-        <v>70</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K27">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J27"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B28" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C28" t="s">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="D28">
         <v>225</v>
@@ -2187,34 +1785,17 @@
       <c r="E28">
         <v>1</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H28">
-        <v>70</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K28">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J28"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B29" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C29" t="s">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="D29">
         <v>225</v>
@@ -2222,34 +1803,17 @@
       <c r="E29">
         <v>1</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H29">
-        <v>70</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K29">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="J29"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B30" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C30" t="s">
-        <v>234</v>
+        <v>277</v>
       </c>
       <c r="D30">
         <v>225</v>
@@ -2257,77 +1821,55 @@
       <c r="E30">
         <v>1</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H30">
-        <v>70</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K30">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="J30"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>278</v>
+      </c>
+      <c r="C31" t="s">
+        <v>279</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G31" t="s">
-        <v>7</v>
-      </c>
-      <c r="H31" t="s">
+      <c r="J31"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>153</v>
+      </c>
+      <c r="B32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G32" t="s">
+        <v>7</v>
+      </c>
+      <c r="H32" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
-        <v>155</v>
-      </c>
-      <c r="B32" t="s">
-        <v>36</v>
-      </c>
-      <c r="E32">
-        <v>1</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G32" t="s">
-        <v>7</v>
-      </c>
-      <c r="H32" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" t="s">
-        <v>235</v>
+        <v>36</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -2339,15 +1881,18 @@
         <v>7</v>
       </c>
       <c r="H33" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>43</v>
+      </c>
+      <c r="C34" t="s">
+        <v>202</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -2359,15 +1904,15 @@
         <v>7</v>
       </c>
       <c r="H34" t="s">
-        <v>18</v>
+        <v>292</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B35" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -2379,18 +1924,15 @@
         <v>7</v>
       </c>
       <c r="H35" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B36" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36" t="s">
-        <v>236</v>
+        <v>46</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -2402,21 +1944,18 @@
         <v>7</v>
       </c>
       <c r="H36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C37" t="s">
-        <v>237</v>
-      </c>
-      <c r="D37">
-        <v>240</v>
+        <v>203</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -2426,14 +1965,23 @@
       </c>
       <c r="G37" t="s">
         <v>7</v>
+      </c>
+      <c r="H37" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>48</v>
+      </c>
+      <c r="C38" t="s">
+        <v>204</v>
+      </c>
+      <c r="D38">
+        <v>240</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -2443,20 +1991,14 @@
       </c>
       <c r="G38" t="s">
         <v>7</v>
-      </c>
-      <c r="H38" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B39" t="s">
-        <v>51</v>
-      </c>
-      <c r="D39">
-        <v>210</v>
+        <v>49</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -2466,14 +2008,20 @@
       </c>
       <c r="G39" t="s">
         <v>7</v>
+      </c>
+      <c r="H39" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="D40">
+        <v>210</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -2483,23 +2031,14 @@
       </c>
       <c r="G40" t="s">
         <v>7</v>
-      </c>
-      <c r="H40" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
-      </c>
-      <c r="C41" t="s">
-        <v>238</v>
-      </c>
-      <c r="D41">
-        <v>250</v>
+        <v>51</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -2509,14 +2048,23 @@
       </c>
       <c r="G41" t="s">
         <v>7</v>
+      </c>
+      <c r="H41" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>52</v>
+      </c>
+      <c r="C42" t="s">
+        <v>205</v>
+      </c>
+      <c r="D42">
+        <v>250</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -2526,17 +2074,14 @@
       </c>
       <c r="G42" t="s">
         <v>7</v>
-      </c>
-      <c r="H42" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B43" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -2548,18 +2093,15 @@
         <v>7</v>
       </c>
       <c r="H43" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
-      </c>
-      <c r="D44">
-        <v>230</v>
+        <v>54</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -2569,40 +2111,38 @@
       </c>
       <c r="G44" t="s">
         <v>7</v>
+      </c>
+      <c r="H44" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>244</v>
+      </c>
+      <c r="C45" t="s">
+        <v>245</v>
+      </c>
+      <c r="D45">
+        <v>250</v>
       </c>
       <c r="E45">
         <v>1</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G45" t="s">
-        <v>7</v>
-      </c>
-      <c r="H45" t="s">
-        <v>35</v>
-      </c>
+      <c r="F45" s="1"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
-      </c>
-      <c r="C46" t="s">
-        <v>239</v>
+        <v>55</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="E46">
         <v>1</v>
@@ -2612,35 +2152,37 @@
       </c>
       <c r="G46" t="s">
         <v>7</v>
-      </c>
-      <c r="H46" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
-      </c>
-      <c r="D47">
-        <v>310</v>
+        <v>56</v>
       </c>
       <c r="E47">
         <v>1</v>
       </c>
-      <c r="F47" s="1"/>
+      <c r="F47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G47" t="s">
+        <v>7</v>
+      </c>
+      <c r="H47" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B48" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C48" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2648,41 +2190,40 @@
       <c r="E48">
         <v>1</v>
       </c>
-      <c r="F48" s="1"/>
+      <c r="F48" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="G48" t="s">
         <v>7</v>
       </c>
       <c r="H48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B49" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="E49">
         <v>1</v>
       </c>
       <c r="F49" s="1"/>
-      <c r="G49" t="s">
-        <v>7</v>
-      </c>
-      <c r="H49" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B50" t="s">
-        <v>81</v>
+        <v>58</v>
+      </c>
+      <c r="C50" t="s">
+        <v>207</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2690,22 +2231,20 @@
       <c r="E50">
         <v>1</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="F50" s="1"/>
       <c r="G50" t="s">
-        <v>171</v>
+        <v>7</v>
       </c>
       <c r="H50" t="s">
-        <v>175</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B51" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2713,22 +2252,20 @@
       <c r="E51">
         <v>1</v>
       </c>
-      <c r="F51" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="F51" s="1"/>
       <c r="G51" t="s">
         <v>7</v>
       </c>
       <c r="H51" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B52" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2740,36 +2277,41 @@
         <v>6</v>
       </c>
       <c r="G52" t="s">
-        <v>7</v>
+        <v>167</v>
       </c>
       <c r="H52" t="s">
-        <v>24</v>
+        <v>171</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B53" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D53">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E53">
         <v>1</v>
       </c>
-      <c r="F53" s="1"/>
+      <c r="F53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G53" t="s">
+        <v>7</v>
+      </c>
+      <c r="H53" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B54" t="s">
-        <v>85</v>
-      </c>
-      <c r="C54" t="s">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2784,44 +2326,33 @@
         <v>7</v>
       </c>
       <c r="H54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B55" t="s">
-        <v>242</v>
-      </c>
-      <c r="C55" t="s">
-        <v>242</v>
+        <v>83</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E55">
         <v>1</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G55" t="s">
-        <v>7</v>
-      </c>
-      <c r="H55" t="s">
-        <v>26</v>
-      </c>
+      <c r="F55" s="1"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B56" t="s">
-        <v>243</v>
+        <v>84</v>
       </c>
       <c r="C56" t="s">
-        <v>243</v>
+        <v>208</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2836,117 +2367,123 @@
         <v>7</v>
       </c>
       <c r="H56" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B57" t="s">
-        <v>86</v>
+        <v>209</v>
+      </c>
+      <c r="C57" t="s">
+        <v>209</v>
       </c>
       <c r="D57">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="E57">
         <v>1</v>
       </c>
-      <c r="F57" s="1"/>
+      <c r="F57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G57" t="s">
+        <v>7</v>
+      </c>
+      <c r="H57" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B58" t="s">
-        <v>118</v>
+        <v>210</v>
+      </c>
+      <c r="C58" t="s">
+        <v>210</v>
       </c>
       <c r="D58">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E58">
         <v>1</v>
       </c>
-      <c r="F58" s="1"/>
+      <c r="F58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G58" t="s">
+        <v>7</v>
+      </c>
+      <c r="H58" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B59" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="D59">
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="E59">
         <v>1</v>
       </c>
-      <c r="F59" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H59">
-        <v>125</v>
-      </c>
+      <c r="F59" s="1"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B60" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D60">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="E60">
         <v>1</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H60">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="F60" s="1"/>
+    </row>
+    <row r="61" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B61" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D61">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E61">
         <v>1</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H61">
-        <v>60</v>
+        <v>280</v>
+      </c>
+      <c r="H61" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B62" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D62">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E62">
         <v>1</v>
@@ -2958,18 +2495,18 @@
         <v>21</v>
       </c>
       <c r="H62">
-        <v>130</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B63" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D63">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="E63">
         <v>1</v>
@@ -2981,15 +2518,15 @@
         <v>21</v>
       </c>
       <c r="H63">
-        <v>135</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B64" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D64">
         <v>50</v>
@@ -3009,10 +2546,10 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B65" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D65">
         <v>65</v>
@@ -3032,86 +2569,86 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B66" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D66">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E66">
         <v>1</v>
       </c>
-      <c r="F66" s="1"/>
+      <c r="F66" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H66">
+        <v>130</v>
+      </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B67" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D67">
+        <v>65</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H67">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A68" t="s">
+        <v>164</v>
+      </c>
+      <c r="B68" t="s">
+        <v>124</v>
+      </c>
+      <c r="D68">
+        <v>65</v>
+      </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
+      <c r="F68" s="1"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A69" t="s">
+        <v>164</v>
+      </c>
+      <c r="B69" t="s">
+        <v>125</v>
+      </c>
+      <c r="D69">
         <v>70</v>
       </c>
-      <c r="E67">
-        <v>1</v>
-      </c>
-      <c r="F67" s="1"/>
-    </row>
-    <row r="68" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A68" t="s">
-        <v>166</v>
-      </c>
-      <c r="B68" t="s">
-        <v>128</v>
-      </c>
-      <c r="D68">
-        <v>85</v>
-      </c>
-      <c r="E68">
-        <v>1</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H68">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A69" t="s">
-        <v>166</v>
-      </c>
-      <c r="B69" t="s">
-        <v>129</v>
-      </c>
-      <c r="D69">
-        <v>85</v>
-      </c>
       <c r="E69">
         <v>1</v>
       </c>
-      <c r="F69" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H69">
-        <v>25</v>
-      </c>
+      <c r="F69" s="1"/>
     </row>
     <row r="70" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B70" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D70">
         <v>85</v>
@@ -3131,10 +2668,10 @@
     </row>
     <row r="71" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B71" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D71">
         <v>85</v>
@@ -3154,13 +2691,13 @@
     </row>
     <row r="72" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B72" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D72">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -3177,13 +2714,13 @@
     </row>
     <row r="73" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B73" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D73">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E73">
         <v>1</v>
@@ -3200,10 +2737,10 @@
     </row>
     <row r="74" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B74" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D74">
         <v>88</v>
@@ -3221,45 +2758,61 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B75" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D75">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="E75">
         <v>1</v>
       </c>
-      <c r="F75" s="1"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="F75" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H75">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B76" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D76">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E76">
         <v>1</v>
       </c>
-      <c r="F76" s="1"/>
+      <c r="F76" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H76">
+        <v>25</v>
+      </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B77" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D77">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="E77">
         <v>1</v>
@@ -3268,13 +2821,13 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B78" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D78">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="E78">
         <v>1</v>
@@ -3283,13 +2836,13 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B79" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D79">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="E79">
         <v>1</v>
@@ -3298,446 +2851,319 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="B80" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="D80">
+        <v>45</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+      <c r="F80" s="1"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A81" t="s">
+        <v>164</v>
+      </c>
+      <c r="B81" t="s">
+        <v>137</v>
+      </c>
+      <c r="D81">
+        <v>150</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+      <c r="F81" s="1"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A82" t="s">
+        <v>164</v>
+      </c>
+      <c r="B82" t="s">
+        <v>282</v>
+      </c>
+      <c r="D82">
+        <v>65</v>
+      </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
+      <c r="F82" s="1"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A83" t="s">
+        <v>164</v>
+      </c>
+      <c r="B83" t="s">
+        <v>283</v>
+      </c>
+      <c r="D83">
+        <v>25</v>
+      </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
+      <c r="F83" s="1"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A84" t="s">
+        <v>152</v>
+      </c>
+      <c r="B84" t="s">
+        <v>145</v>
+      </c>
+      <c r="D84">
         <v>285</v>
-      </c>
-      <c r="E80">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A81" t="s">
-        <v>154</v>
-      </c>
-      <c r="B81" t="s">
-        <v>148</v>
-      </c>
-      <c r="D81">
-        <v>325</v>
-      </c>
-      <c r="E81">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A82" t="s">
-        <v>154</v>
-      </c>
-      <c r="B82" t="s">
-        <v>149</v>
-      </c>
-      <c r="D82">
-        <v>325</v>
-      </c>
-      <c r="E82">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A83" t="s">
-        <v>154</v>
-      </c>
-      <c r="B83" t="s">
-        <v>150</v>
-      </c>
-      <c r="D83">
-        <v>335</v>
-      </c>
-      <c r="E83">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A84" t="s">
-        <v>154</v>
-      </c>
-      <c r="B84" t="s">
-        <v>151</v>
-      </c>
-      <c r="D84">
-        <v>340</v>
       </c>
       <c r="E84">
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B85" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D85">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="E85">
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B86" t="s">
+        <v>147</v>
+      </c>
+      <c r="D86">
+        <v>325</v>
+      </c>
+      <c r="E86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A87" t="s">
+        <v>152</v>
+      </c>
+      <c r="B87" t="s">
+        <v>148</v>
+      </c>
+      <c r="D87">
+        <v>335</v>
+      </c>
+      <c r="E87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A88" t="s">
+        <v>152</v>
+      </c>
+      <c r="B88" t="s">
+        <v>149</v>
+      </c>
+      <c r="D88">
+        <v>340</v>
+      </c>
+      <c r="E88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A89" t="s">
+        <v>152</v>
+      </c>
+      <c r="B89" t="s">
+        <v>150</v>
+      </c>
+      <c r="D89">
+        <v>350</v>
+      </c>
+      <c r="E89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A90" t="s">
+        <v>151</v>
+      </c>
+      <c r="B90" t="s">
+        <v>40</v>
+      </c>
+      <c r="C90" t="s">
+        <v>211</v>
+      </c>
+      <c r="D90">
+        <v>260</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A91" t="s">
+        <v>151</v>
+      </c>
+      <c r="B91" t="s">
         <v>41</v>
       </c>
-      <c r="C86" t="s">
-        <v>244</v>
-      </c>
-      <c r="D86">
+      <c r="C91" t="s">
+        <v>212</v>
+      </c>
+      <c r="D91">
+        <v>330</v>
+      </c>
+      <c r="E91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A92" t="s">
+        <v>151</v>
+      </c>
+      <c r="B92" t="s">
+        <v>36</v>
+      </c>
+      <c r="D92">
+        <v>230</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A93" t="s">
+        <v>151</v>
+      </c>
+      <c r="B93" t="s">
+        <v>42</v>
+      </c>
+      <c r="C93" t="s">
+        <v>213</v>
+      </c>
+      <c r="D93">
+        <v>240</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A94" t="s">
+        <v>151</v>
+      </c>
+      <c r="B94" t="s">
+        <v>43</v>
+      </c>
+      <c r="C94" t="s">
+        <v>202</v>
+      </c>
+      <c r="D94">
+        <v>220</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A95" t="s">
+        <v>151</v>
+      </c>
+      <c r="B95" t="s">
+        <v>246</v>
+      </c>
+      <c r="D95">
         <v>260</v>
       </c>
-      <c r="E86">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A87" t="s">
-        <v>153</v>
-      </c>
-      <c r="B87" t="s">
-        <v>42</v>
-      </c>
-      <c r="C87" t="s">
+      <c r="E95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A96" t="s">
+        <v>151</v>
+      </c>
+      <c r="B96" t="s">
+        <v>37</v>
+      </c>
+      <c r="D96">
+        <v>310</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A97" t="s">
+        <v>151</v>
+      </c>
+      <c r="B97" t="s">
+        <v>38</v>
+      </c>
+      <c r="D97">
+        <v>280</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A98" t="s">
+        <v>151</v>
+      </c>
+      <c r="B98" t="s">
+        <v>39</v>
+      </c>
+      <c r="D98">
         <v>245</v>
       </c>
-      <c r="D87">
-        <v>330</v>
-      </c>
-      <c r="E87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A88" t="s">
-        <v>153</v>
-      </c>
-      <c r="B88" t="s">
-        <v>36</v>
-      </c>
-      <c r="D88">
-        <v>230</v>
-      </c>
-      <c r="E88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A89" t="s">
-        <v>153</v>
-      </c>
-      <c r="B89" t="s">
-        <v>43</v>
-      </c>
-      <c r="C89" t="s">
-        <v>246</v>
-      </c>
-      <c r="D89">
-        <v>240</v>
-      </c>
-      <c r="E89">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A90" t="s">
-        <v>153</v>
-      </c>
-      <c r="B90" t="s">
-        <v>44</v>
-      </c>
-      <c r="C90" t="s">
-        <v>235</v>
-      </c>
-      <c r="D90">
-        <v>220</v>
-      </c>
-      <c r="E90">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A91" t="s">
-        <v>153</v>
-      </c>
-      <c r="B91" t="s">
-        <v>37</v>
-      </c>
-      <c r="D91">
-        <v>260</v>
-      </c>
-      <c r="E91">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A92" t="s">
-        <v>153</v>
-      </c>
-      <c r="B92" t="s">
-        <v>38</v>
-      </c>
-      <c r="D92">
-        <v>310</v>
-      </c>
-      <c r="E92">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A93" t="s">
-        <v>153</v>
-      </c>
-      <c r="B93" t="s">
-        <v>39</v>
-      </c>
-      <c r="D93">
-        <v>280</v>
-      </c>
-      <c r="E93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A94" t="s">
-        <v>153</v>
-      </c>
-      <c r="B94" t="s">
-        <v>40</v>
-      </c>
-      <c r="D94">
-        <v>245</v>
-      </c>
-      <c r="E94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A95" t="s">
-        <v>161</v>
-      </c>
-      <c r="B95" t="s">
+      <c r="E98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A99" t="s">
+        <v>159</v>
+      </c>
+      <c r="B99" t="s">
+        <v>86</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G99" t="s">
+        <v>7</v>
+      </c>
+      <c r="H99" t="s">
+        <v>27</v>
+      </c>
+      <c r="J99"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A100" t="s">
+        <v>159</v>
+      </c>
+      <c r="B100" t="s">
         <v>87</v>
       </c>
-      <c r="D95">
-        <v>0</v>
-      </c>
-      <c r="E95">
-        <v>1</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G95" t="s">
-        <v>7</v>
-      </c>
-      <c r="H95" t="s">
-        <v>27</v>
-      </c>
-      <c r="I95" t="s">
-        <v>261</v>
-      </c>
-      <c r="J95" t="s">
-        <v>261</v>
-      </c>
-      <c r="K95">
-        <v>50</v>
-      </c>
-      <c r="L95" t="s">
-        <v>262</v>
-      </c>
-      <c r="M95" t="s">
-        <v>262</v>
-      </c>
-      <c r="N95">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A96" t="s">
-        <v>161</v>
-      </c>
-      <c r="B96" t="s">
-        <v>88</v>
-      </c>
-      <c r="C96" t="s">
-        <v>247</v>
-      </c>
-      <c r="D96">
-        <v>0</v>
-      </c>
-      <c r="E96">
-        <v>1</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G96" t="s">
-        <v>7</v>
-      </c>
-      <c r="H96" t="s">
-        <v>28</v>
-      </c>
-      <c r="I96" t="s">
-        <v>261</v>
-      </c>
-      <c r="J96" t="s">
-        <v>261</v>
-      </c>
-      <c r="K96">
-        <v>50</v>
-      </c>
-      <c r="L96" t="s">
-        <v>262</v>
-      </c>
-      <c r="M96" t="s">
-        <v>262</v>
-      </c>
-      <c r="N96">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A97" t="s">
-        <v>161</v>
-      </c>
-      <c r="B97" t="s">
-        <v>89</v>
-      </c>
-      <c r="C97" t="s">
-        <v>248</v>
-      </c>
-      <c r="D97">
-        <v>0</v>
-      </c>
-      <c r="E97">
-        <v>1</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G97" t="s">
-        <v>7</v>
-      </c>
-      <c r="H97" t="s">
-        <v>28</v>
-      </c>
-      <c r="I97" t="s">
-        <v>261</v>
-      </c>
-      <c r="J97" t="s">
-        <v>261</v>
-      </c>
-      <c r="K97">
-        <v>50</v>
-      </c>
-      <c r="L97" t="s">
-        <v>262</v>
-      </c>
-      <c r="M97" t="s">
-        <v>262</v>
-      </c>
-      <c r="N97">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A98" t="s">
-        <v>161</v>
-      </c>
-      <c r="B98" t="s">
-        <v>90</v>
-      </c>
-      <c r="D98">
-        <v>0</v>
-      </c>
-      <c r="E98">
-        <v>1</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G98" t="s">
-        <v>7</v>
-      </c>
-      <c r="H98" t="s">
-        <v>28</v>
-      </c>
-      <c r="I98" t="s">
-        <v>261</v>
-      </c>
-      <c r="J98" t="s">
-        <v>261</v>
-      </c>
-      <c r="K98">
-        <v>50</v>
-      </c>
-      <c r="L98" t="s">
-        <v>262</v>
-      </c>
-      <c r="M98" t="s">
-        <v>262</v>
-      </c>
-      <c r="N98">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A99" t="s">
-        <v>161</v>
-      </c>
-      <c r="B99" t="s">
-        <v>252</v>
-      </c>
-      <c r="C99" t="s">
-        <v>253</v>
-      </c>
-      <c r="D99">
-        <v>0</v>
-      </c>
-      <c r="E99">
-        <v>1</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G99" t="s">
-        <v>7</v>
-      </c>
-      <c r="H99" t="s">
-        <v>28</v>
-      </c>
-      <c r="I99" t="s">
-        <v>261</v>
-      </c>
-      <c r="J99" t="s">
-        <v>261</v>
-      </c>
-      <c r="K99">
-        <v>50</v>
-      </c>
-      <c r="L99" t="s">
-        <v>262</v>
-      </c>
-      <c r="M99" t="s">
-        <v>262</v>
-      </c>
-      <c r="N99">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A100" t="s">
-        <v>161</v>
-      </c>
-      <c r="B100" t="s">
-        <v>91</v>
+      <c r="C100" t="s">
+        <v>214</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3754,261 +3180,200 @@
       <c r="H100" t="s">
         <v>28</v>
       </c>
-      <c r="I100" t="s">
-        <v>261</v>
-      </c>
-      <c r="J100" t="s">
-        <v>261</v>
-      </c>
-      <c r="K100">
-        <v>50</v>
-      </c>
-      <c r="L100" t="s">
-        <v>262</v>
-      </c>
-      <c r="M100" t="s">
-        <v>262</v>
-      </c>
-      <c r="N100">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="J100"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B101" t="s">
+        <v>88</v>
+      </c>
+      <c r="C101" t="s">
+        <v>215</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G101" t="s">
+        <v>7</v>
+      </c>
+      <c r="H101" t="s">
+        <v>28</v>
+      </c>
+      <c r="J101"/>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A102" t="s">
+        <v>159</v>
+      </c>
+      <c r="B102" t="s">
+        <v>89</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G102" t="s">
+        <v>7</v>
+      </c>
+      <c r="H102" t="s">
+        <v>28</v>
+      </c>
+      <c r="J102"/>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A103" t="s">
+        <v>159</v>
+      </c>
+      <c r="B103" t="s">
+        <v>219</v>
+      </c>
+      <c r="C103" t="s">
+        <v>220</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>1</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G103" t="s">
+        <v>7</v>
+      </c>
+      <c r="H103" t="s">
+        <v>28</v>
+      </c>
+      <c r="J103"/>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A104" t="s">
+        <v>159</v>
+      </c>
+      <c r="B104" t="s">
+        <v>90</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <v>1</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G104" t="s">
+        <v>7</v>
+      </c>
+      <c r="H104" t="s">
+        <v>28</v>
+      </c>
+      <c r="J104"/>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
+        <v>159</v>
+      </c>
+      <c r="B105" t="s">
+        <v>91</v>
+      </c>
+      <c r="C105" t="s">
+        <v>216</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G105" t="s">
+        <v>167</v>
+      </c>
+      <c r="H105" t="s">
+        <v>169</v>
+      </c>
+      <c r="J105"/>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>159</v>
+      </c>
+      <c r="B106" t="s">
         <v>92</v>
       </c>
-      <c r="C101" t="s">
-        <v>249</v>
-      </c>
-      <c r="D101">
-        <v>0</v>
-      </c>
-      <c r="E101">
-        <v>1</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G101" t="s">
-        <v>171</v>
-      </c>
-      <c r="H101" t="s">
-        <v>173</v>
-      </c>
-      <c r="I101" t="s">
-        <v>261</v>
-      </c>
-      <c r="J101" t="s">
-        <v>261</v>
-      </c>
-      <c r="K101">
-        <v>50</v>
-      </c>
-      <c r="L101" t="s">
-        <v>262</v>
-      </c>
-      <c r="M101" t="s">
-        <v>262</v>
-      </c>
-      <c r="N101">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A102" t="s">
-        <v>161</v>
-      </c>
-      <c r="B102" t="s">
+      <c r="C106" t="s">
+        <v>217</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>1</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G106" t="s">
+        <v>167</v>
+      </c>
+      <c r="H106" t="s">
+        <v>169</v>
+      </c>
+      <c r="J106"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A107" t="s">
+        <v>159</v>
+      </c>
+      <c r="B107" t="s">
         <v>93</v>
       </c>
-      <c r="C102" t="s">
-        <v>250</v>
-      </c>
-      <c r="D102">
-        <v>0</v>
-      </c>
-      <c r="E102">
-        <v>1</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G102" t="s">
-        <v>171</v>
-      </c>
-      <c r="H102" t="s">
-        <v>173</v>
-      </c>
-      <c r="I102" t="s">
-        <v>261</v>
-      </c>
-      <c r="J102" t="s">
-        <v>261</v>
-      </c>
-      <c r="K102">
-        <v>50</v>
-      </c>
-      <c r="L102" t="s">
-        <v>262</v>
-      </c>
-      <c r="M102" t="s">
-        <v>262</v>
-      </c>
-      <c r="N102">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A103" t="s">
-        <v>161</v>
-      </c>
-      <c r="B103" t="s">
+      <c r="C107" t="s">
+        <v>218</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <v>1</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G107" t="s">
+        <v>167</v>
+      </c>
+      <c r="H107" t="s">
+        <v>169</v>
+      </c>
+      <c r="J107"/>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A108" t="s">
+        <v>160</v>
+      </c>
+      <c r="B108" t="s">
         <v>94</v>
       </c>
-      <c r="C103" t="s">
-        <v>251</v>
-      </c>
-      <c r="D103">
-        <v>0</v>
-      </c>
-      <c r="E103">
-        <v>1</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G103" t="s">
-        <v>171</v>
-      </c>
-      <c r="H103" t="s">
-        <v>173</v>
-      </c>
-      <c r="I103" t="s">
-        <v>261</v>
-      </c>
-      <c r="J103" t="s">
-        <v>261</v>
-      </c>
-      <c r="K103">
-        <v>50</v>
-      </c>
-      <c r="L103" t="s">
-        <v>262</v>
-      </c>
-      <c r="M103" t="s">
-        <v>262</v>
-      </c>
-      <c r="N103">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A104" t="s">
-        <v>162</v>
-      </c>
-      <c r="B104" t="s">
-        <v>95</v>
-      </c>
-      <c r="C104" t="s">
-        <v>254</v>
-      </c>
-      <c r="D104">
-        <v>0</v>
-      </c>
-      <c r="E104">
-        <v>1</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G104" t="s">
-        <v>7</v>
-      </c>
-      <c r="H104" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A105" t="s">
-        <v>162</v>
-      </c>
-      <c r="B105" t="s">
-        <v>96</v>
-      </c>
-      <c r="D105">
-        <v>0</v>
-      </c>
-      <c r="E105">
-        <v>1</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G105" t="s">
-        <v>7</v>
-      </c>
-      <c r="H105" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A106" t="s">
-        <v>162</v>
-      </c>
-      <c r="B106" t="s">
-        <v>97</v>
-      </c>
-      <c r="D106">
-        <v>0</v>
-      </c>
-      <c r="E106">
-        <v>1</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G106" t="s">
-        <v>7</v>
-      </c>
-      <c r="H106" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A107" t="s">
-        <v>162</v>
-      </c>
-      <c r="B107" t="s">
-        <v>98</v>
-      </c>
-      <c r="D107">
-        <v>0</v>
-      </c>
-      <c r="E107">
-        <v>1</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G107" t="s">
-        <v>7</v>
-      </c>
-      <c r="H107" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A108" t="s">
-        <v>162</v>
-      </c>
-      <c r="B108" t="s">
-        <v>99</v>
-      </c>
       <c r="C108" t="s">
-        <v>255</v>
+        <v>221</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -4026,12 +3391,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B109" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -4046,15 +3411,15 @@
         <v>7</v>
       </c>
       <c r="H109" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B110" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -4069,15 +3434,15 @@
         <v>7</v>
       </c>
       <c r="H110" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B111" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -4092,18 +3457,18 @@
         <v>7</v>
       </c>
       <c r="H111" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B112" t="s">
-        <v>68</v>
+        <v>247</v>
       </c>
       <c r="C112" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -4118,18 +3483,15 @@
         <v>7</v>
       </c>
       <c r="H112" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B113" t="s">
-        <v>69</v>
-      </c>
-      <c r="C113" t="s">
-        <v>257</v>
+        <v>98</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -4144,18 +3506,15 @@
         <v>7</v>
       </c>
       <c r="H113" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B114" t="s">
-        <v>70</v>
-      </c>
-      <c r="C114" t="s">
-        <v>258</v>
+        <v>65</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -4170,18 +3529,15 @@
         <v>7</v>
       </c>
       <c r="H114" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B115" t="s">
-        <v>71</v>
-      </c>
-      <c r="C115" t="s">
-        <v>259</v>
+        <v>66</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -4196,18 +3552,18 @@
         <v>7</v>
       </c>
       <c r="H115" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B116" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C116" t="s">
-        <v>260</v>
+        <v>222</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -4227,10 +3583,13 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B117" t="s">
-        <v>73</v>
+        <v>68</v>
+      </c>
+      <c r="C117" t="s">
+        <v>223</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -4242,33 +3601,47 @@
         <v>6</v>
       </c>
       <c r="G117" t="s">
-        <v>171</v>
+        <v>7</v>
       </c>
       <c r="H117" t="s">
-        <v>172</v>
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B118" t="s">
-        <v>174</v>
+        <v>69</v>
+      </c>
+      <c r="C118" t="s">
+        <v>224</v>
       </c>
       <c r="D118">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E118">
         <v>1</v>
       </c>
-      <c r="F118" s="1"/>
+      <c r="F118" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G118" t="s">
+        <v>7</v>
+      </c>
+      <c r="H118" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B119" t="s">
-        <v>40</v>
+        <v>70</v>
+      </c>
+      <c r="C119" t="s">
+        <v>225</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -4283,18 +3656,18 @@
         <v>7</v>
       </c>
       <c r="H119" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B120" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C120" t="s">
-        <v>263</v>
+        <v>226</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -4309,18 +3682,15 @@
         <v>7</v>
       </c>
       <c r="H120" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B121" t="s">
-        <v>75</v>
-      </c>
-      <c r="C121" t="s">
-        <v>264</v>
+        <v>72</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -4332,214 +3702,203 @@
         <v>6</v>
       </c>
       <c r="G121" t="s">
-        <v>7</v>
+        <v>167</v>
       </c>
       <c r="H121" t="s">
-        <v>15</v>
+        <v>168</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B122" t="s">
-        <v>76</v>
-      </c>
-      <c r="C122" t="s">
-        <v>265</v>
+        <v>170</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E122">
         <v>1</v>
       </c>
-      <c r="F122" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G122" t="s">
-        <v>7</v>
-      </c>
-      <c r="H122" t="s">
-        <v>13</v>
-      </c>
+      <c r="F122" s="1"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B123" t="s">
-        <v>77</v>
-      </c>
-      <c r="C123" t="s">
-        <v>266</v>
+        <v>39</v>
       </c>
       <c r="D123">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E123">
         <v>1</v>
       </c>
-      <c r="F123" s="1"/>
+      <c r="F123" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G123" t="s">
+        <v>7</v>
+      </c>
+      <c r="H123" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B124" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C124" t="s">
-        <v>267</v>
+        <v>227</v>
       </c>
       <c r="D124">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E124">
         <v>1</v>
       </c>
-      <c r="F124" s="1"/>
+      <c r="F124" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G124" t="s">
+        <v>7</v>
+      </c>
+      <c r="H124" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B125" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C125" t="s">
-        <v>268</v>
+        <v>228</v>
       </c>
       <c r="D125">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="E125">
         <v>1</v>
       </c>
-      <c r="F125" s="1"/>
+      <c r="F125" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G125" t="s">
+        <v>7</v>
+      </c>
+      <c r="H125" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B126" t="s">
-        <v>80</v>
+        <v>75</v>
+      </c>
+      <c r="C126" t="s">
+        <v>229</v>
       </c>
       <c r="D126">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E126">
         <v>1</v>
       </c>
-      <c r="F126" s="1"/>
+      <c r="F126" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G126" t="s">
+        <v>7</v>
+      </c>
+      <c r="H126" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B127" t="s">
-        <v>101</v>
+        <v>76</v>
+      </c>
+      <c r="C127" t="s">
+        <v>230</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="E127">
         <v>1</v>
       </c>
-      <c r="F127" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G127" t="s">
-        <v>7</v>
-      </c>
-      <c r="H127" t="s">
-        <v>16</v>
-      </c>
+      <c r="F127" s="1"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B128" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="C128" t="s">
-        <v>269</v>
+        <v>231</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="E128">
         <v>1</v>
       </c>
-      <c r="F128" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G128" t="s">
-        <v>7</v>
-      </c>
-      <c r="H128" t="s">
-        <v>16</v>
-      </c>
+      <c r="F128" s="1"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B129" t="s">
-        <v>103</v>
+        <v>78</v>
+      </c>
+      <c r="C129" t="s">
+        <v>232</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="E129">
         <v>1</v>
       </c>
-      <c r="F129" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G129" t="s">
-        <v>7</v>
-      </c>
-      <c r="H129" t="s">
-        <v>17</v>
-      </c>
+      <c r="F129" s="1"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B130" t="s">
-        <v>104</v>
-      </c>
-      <c r="C130" t="s">
-        <v>270</v>
+        <v>79</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="E130">
         <v>1</v>
       </c>
-      <c r="F130" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G130" t="s">
-        <v>7</v>
-      </c>
-      <c r="H130" t="s">
-        <v>17</v>
-      </c>
+      <c r="F130" s="1"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B131" t="s">
-        <v>105</v>
-      </c>
-      <c r="C131" t="s">
-        <v>271</v>
+        <v>99</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -4554,18 +3913,18 @@
         <v>7</v>
       </c>
       <c r="H131" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B132" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C132" t="s">
-        <v>272</v>
+        <v>233</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -4585,10 +3944,10 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B133" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -4608,66 +3967,111 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B134" t="s">
-        <v>108</v>
+        <v>102</v>
+      </c>
+      <c r="C134" t="s">
+        <v>234</v>
       </c>
       <c r="D134">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="E134">
         <v>1</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G134" t="s">
+        <v>7</v>
+      </c>
+      <c r="H134" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B135" t="s">
-        <v>109</v>
+        <v>103</v>
+      </c>
+      <c r="C135" t="s">
+        <v>235</v>
       </c>
       <c r="D135">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="E135">
         <v>1</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G135" t="s">
+        <v>7</v>
+      </c>
+      <c r="H135" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B136" t="s">
-        <v>110</v>
+        <v>104</v>
+      </c>
+      <c r="C136" t="s">
+        <v>236</v>
       </c>
       <c r="D136">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="E136">
         <v>1</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G136" t="s">
+        <v>7</v>
+      </c>
+      <c r="H136" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B137" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D137">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="E137">
         <v>1</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G137" t="s">
+        <v>7</v>
+      </c>
+      <c r="H137" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B138" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D138">
         <v>295</v>
@@ -4678,13 +4082,13 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B139" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D139">
-        <v>240</v>
+        <v>295</v>
       </c>
       <c r="E139">
         <v>1</v>
@@ -4692,13 +4096,13 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B140" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D140">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E140">
         <v>1</v>
@@ -4706,13 +4110,13 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B141" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D141">
-        <v>290</v>
+        <v>245</v>
       </c>
       <c r="E141">
         <v>1</v>
@@ -4720,13 +4124,13 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B142" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D142">
-        <v>240</v>
+        <v>295</v>
       </c>
       <c r="E142">
         <v>1</v>
@@ -4734,10 +4138,10 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B143" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D143">
         <v>240</v>
@@ -4748,13 +4152,13 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B144" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="D144">
-        <v>350</v>
+        <v>290</v>
       </c>
       <c r="E144">
         <v>1</v>
@@ -4762,13 +4166,13 @@
     </row>
     <row r="145" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B145" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="D145">
-        <v>350</v>
+        <v>290</v>
       </c>
       <c r="E145">
         <v>1</v>
@@ -4776,13 +4180,13 @@
     </row>
     <row r="146" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B146" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="D146">
-        <v>370</v>
+        <v>240</v>
       </c>
       <c r="E146">
         <v>1</v>
@@ -4790,13 +4194,13 @@
     </row>
     <row r="147" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B147" t="s">
-        <v>39</v>
+        <v>115</v>
       </c>
       <c r="D147">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="E147">
         <v>1</v>
@@ -4804,13 +4208,10 @@
     </row>
     <row r="148" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B148" t="s">
-        <v>64</v>
-      </c>
-      <c r="C148" t="s">
-        <v>273</v>
+        <v>60</v>
       </c>
       <c r="D148">
         <v>350</v>
@@ -4821,13 +4222,13 @@
     </row>
     <row r="149" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B149" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D149">
-        <v>35</v>
+        <v>350</v>
       </c>
       <c r="E149">
         <v>1</v>
@@ -4835,85 +4236,75 @@
     </row>
     <row r="150" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>145</v>
-      </c>
-      <c r="C150" t="s">
-        <v>274</v>
+        <v>62</v>
       </c>
       <c r="D150">
-        <v>100</v>
+        <v>370</v>
       </c>
       <c r="E150">
         <v>1</v>
       </c>
-      <c r="P150" s="1"/>
     </row>
     <row r="151" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="B151" t="s">
-        <v>140</v>
-      </c>
-      <c r="C151" t="s">
-        <v>275</v>
+        <v>38</v>
       </c>
       <c r="D151">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="E151">
         <v>1</v>
       </c>
-      <c r="P151" s="1"/>
     </row>
     <row r="152" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="B152" t="s">
-        <v>141</v>
+        <v>63</v>
       </c>
       <c r="C152" t="s">
-        <v>276</v>
+        <v>237</v>
       </c>
       <c r="D152">
-        <v>130</v>
+        <v>350</v>
       </c>
       <c r="E152">
         <v>1</v>
       </c>
-      <c r="P152" s="1"/>
     </row>
     <row r="153" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="B153" t="s">
-        <v>142</v>
-      </c>
-      <c r="C153" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="D153">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="E153">
         <v>1</v>
       </c>
-      <c r="P153" s="1"/>
     </row>
     <row r="154" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B154" t="s">
         <v>143</v>
       </c>
+      <c r="C154" t="s">
+        <v>238</v>
+      </c>
       <c r="D154">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="E154">
         <v>1</v>
@@ -4922,39 +4313,209 @@
     </row>
     <row r="155" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B155" t="s">
-        <v>144</v>
+        <v>138</v>
+      </c>
+      <c r="C155" t="s">
+        <v>239</v>
       </c>
       <c r="D155">
+        <v>100</v>
+      </c>
+      <c r="E155">
+        <v>1</v>
+      </c>
+      <c r="P155" s="1"/>
+    </row>
+    <row r="156" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A156" t="s">
+        <v>166</v>
+      </c>
+      <c r="B156" t="s">
+        <v>139</v>
+      </c>
+      <c r="C156" t="s">
+        <v>240</v>
+      </c>
+      <c r="D156">
+        <v>130</v>
+      </c>
+      <c r="E156">
+        <v>1</v>
+      </c>
+      <c r="P156" s="1"/>
+    </row>
+    <row r="157" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A157" t="s">
+        <v>166</v>
+      </c>
+      <c r="B157" t="s">
+        <v>140</v>
+      </c>
+      <c r="C157" t="s">
+        <v>85</v>
+      </c>
+      <c r="D157">
+        <v>130</v>
+      </c>
+      <c r="E157">
+        <v>1</v>
+      </c>
+      <c r="P157" s="1"/>
+    </row>
+    <row r="158" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A158" t="s">
+        <v>166</v>
+      </c>
+      <c r="B158" t="s">
+        <v>141</v>
+      </c>
+      <c r="D158">
+        <v>55</v>
+      </c>
+      <c r="E158">
+        <v>1</v>
+      </c>
+      <c r="P158" s="1"/>
+    </row>
+    <row r="159" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A159" t="s">
+        <v>166</v>
+      </c>
+      <c r="B159" t="s">
+        <v>142</v>
+      </c>
+      <c r="D159">
         <v>25</v>
       </c>
-      <c r="E155">
-        <v>1</v>
-      </c>
-      <c r="P155" s="1"/>
-    </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="P156" t="str">
-        <f xml:space="preserve"> PROPER(R156)</f>
+      <c r="E159">
+        <v>1</v>
+      </c>
+      <c r="P159" s="1"/>
+    </row>
+    <row r="160" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A160" t="s">
+        <v>158</v>
+      </c>
+      <c r="B160" t="s">
+        <v>285</v>
+      </c>
+      <c r="D160">
+        <v>0</v>
+      </c>
+      <c r="E160">
+        <v>1</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G160" t="s">
+        <v>167</v>
+      </c>
+      <c r="H160" t="s">
+        <v>284</v>
+      </c>
+      <c r="P160" t="str">
+        <f xml:space="preserve"> PROPER(R160)</f>
         <v/>
       </c>
-      <c r="T156" s="1"/>
-    </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="P157" t="str">
-        <f xml:space="preserve"> PROPER(R157)</f>
+      <c r="T160" s="1"/>
+    </row>
+    <row r="161" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A161" t="s">
+        <v>158</v>
+      </c>
+      <c r="B161" t="s">
+        <v>289</v>
+      </c>
+      <c r="D161">
+        <v>200</v>
+      </c>
+      <c r="E161">
+        <v>1</v>
+      </c>
+      <c r="P161" t="str">
+        <f xml:space="preserve"> PROPER(R161)</f>
         <v/>
       </c>
-      <c r="T157" s="1"/>
-    </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="P158" t="str">
-        <f xml:space="preserve"> PROPER(R158)</f>
+      <c r="T161" s="1"/>
+    </row>
+    <row r="162" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A162" t="s">
+        <v>158</v>
+      </c>
+      <c r="B162" t="s">
+        <v>288</v>
+      </c>
+      <c r="D162">
+        <v>55</v>
+      </c>
+      <c r="E162">
+        <v>1</v>
+      </c>
+      <c r="P162" t="str">
+        <f xml:space="preserve"> PROPER(R162)</f>
         <v/>
       </c>
-      <c r="T158" s="1"/>
+      <c r="T162" s="1"/>
+    </row>
+    <row r="163" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A163" t="s">
+        <v>158</v>
+      </c>
+      <c r="B163" t="s">
+        <v>286</v>
+      </c>
+      <c r="D163">
+        <v>80</v>
+      </c>
+      <c r="E163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A164" t="s">
+        <v>158</v>
+      </c>
+      <c r="B164" t="s">
+        <v>287</v>
+      </c>
+      <c r="D164">
+        <v>120</v>
+      </c>
+      <c r="E164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A165" t="s">
+        <v>158</v>
+      </c>
+      <c r="B165" t="s">
+        <v>290</v>
+      </c>
+      <c r="D165">
+        <v>50</v>
+      </c>
+      <c r="E165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A166" t="s">
+        <v>158</v>
+      </c>
+      <c r="B166" t="s">
+        <v>291</v>
+      </c>
+      <c r="D166">
+        <v>180</v>
+      </c>
+      <c r="E166">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/palacio_royal_09_12_2026.xlsx
+++ b/data/palacio_royal_09_12_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\renha\workspace\projects\big_boss_bro\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42221D6B-1F3D-4982-9A47-90F5958DA723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92147051-7ACD-4855-A7BF-C8E65DFAB503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="319">
   <si>
     <t>种类</t>
   </si>
@@ -69,9 +69,6 @@
     <t>140/200</t>
   </si>
   <si>
-    <t>140/203</t>
-  </si>
-  <si>
     <t>130/180</t>
   </si>
   <si>
@@ -99,12 +96,6 @@
     <t>200/310</t>
   </si>
   <si>
-    <t>200/300</t>
-  </si>
-  <si>
-    <t>JARRA</t>
-  </si>
-  <si>
     <t>EXTRA BOBA</t>
   </si>
   <si>
@@ -309,9 +300,6 @@
     <t>Caldo Cantones</t>
   </si>
   <si>
-    <t>Clado Mandarin</t>
-  </si>
-  <si>
     <t>Caldo De Pollo</t>
   </si>
   <si>
@@ -327,9 +315,6 @@
     <t>Camaron Almendrado</t>
   </si>
   <si>
-    <t>Camaroncon Brocoli</t>
-  </si>
-  <si>
     <t>Camaron Enchilado</t>
   </si>
   <si>
@@ -384,9 +369,6 @@
     <t>Tofu Con Verduras</t>
   </si>
   <si>
-    <t>Tofu Kunpo</t>
-  </si>
-  <si>
     <t>Sodas</t>
   </si>
   <si>
@@ -543,9 +525,6 @@
     <t>Chico/Mediano/Grande</t>
   </si>
   <si>
-    <t>50/140/150</t>
-  </si>
-  <si>
     <t>50/120/180</t>
   </si>
   <si>
@@ -888,9 +867,6 @@
     <t>Topo Chico</t>
   </si>
   <si>
-    <t>Botella Agua</t>
-  </si>
-  <si>
     <t>90/120/150</t>
   </si>
   <si>
@@ -903,9 +879,6 @@
     <t>Mochi</t>
   </si>
   <si>
-    <t>Boba Latte</t>
-  </si>
-  <si>
     <t>Te Caliente Pac</t>
   </si>
   <si>
@@ -915,7 +888,112 @@
     <t>Ciruela</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>Chow Mein Verduras</t>
+  </si>
+  <si>
+    <t>Camaron Cantonese</t>
+  </si>
+  <si>
+    <t>Camaron con Brocoli</t>
+  </si>
+  <si>
+    <t>Camaron Brocoli</t>
+  </si>
+  <si>
+    <t>Agua</t>
+  </si>
+  <si>
+    <t>Hongo Kung Pao</t>
+  </si>
+  <si>
+    <t>Juge Valle</t>
+  </si>
+  <si>
+    <t>VASO/JARRA</t>
+  </si>
+  <si>
+    <t>70/130</t>
+  </si>
+  <si>
+    <t>90/150</t>
+  </si>
+  <si>
+    <t>65/150/200</t>
+  </si>
+  <si>
+    <t>50/180</t>
+  </si>
+  <si>
+    <t>65/140/200</t>
+  </si>
+  <si>
+    <t>Coco Smoothie</t>
+  </si>
+  <si>
+    <t>20/35</t>
+  </si>
+  <si>
+    <t>Caldo Mandarin</t>
+  </si>
+  <si>
+    <t>Boba Lata</t>
+  </si>
+  <si>
+    <t>Lonche Chow Mein Cantonese</t>
+  </si>
+  <si>
+    <t>L# Chow Mein Cantonese</t>
+  </si>
+  <si>
+    <t>50/90/150</t>
+  </si>
+  <si>
+    <t>Sizzling de 3 sabores</t>
+  </si>
+  <si>
+    <t>Tofu Kung Pao</t>
+  </si>
+  <si>
+    <t>50/130/180</t>
+  </si>
+  <si>
+    <t>Bloody Mary</t>
+  </si>
+  <si>
+    <t>Cafe con Leche</t>
+  </si>
+  <si>
+    <t>CAGUAMA</t>
+  </si>
+  <si>
+    <t>Jazmine Green Tea</t>
+  </si>
+  <si>
+    <t>MICHElADA</t>
+  </si>
+  <si>
+    <t>Pina Colada</t>
+  </si>
+  <si>
+    <t>Sangria Prepararda</t>
+  </si>
+  <si>
+    <t>Thai Tea</t>
+  </si>
+  <si>
+    <t>Pescado Enchilado</t>
+  </si>
+  <si>
+    <t>Grande</t>
+  </si>
+  <si>
+    <t>Tequila Shot</t>
+  </si>
+  <si>
+    <t>VAIIE FRUI</t>
+  </si>
+  <si>
+    <t>VINO MINI</t>
   </si>
 </sst>
 </file>
@@ -1242,7 +1320,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T166"/>
+  <dimension ref="A1:T185"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="27.3046875" bestFit="1" customWidth="1"/>
@@ -1265,13 +1343,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>2</v>
@@ -1289,27 +1367,27 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L1" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="M1" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="N1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C2" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="D2">
         <v>160</v>
@@ -1321,13 +1399,13 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B3" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C3" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D3">
         <v>160</v>
@@ -1339,13 +1417,13 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B4" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="D4">
         <v>175</v>
@@ -1357,13 +1435,13 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B5" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C5" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="D5">
         <v>180</v>
@@ -1375,13 +1453,13 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B6" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D6">
         <v>165</v>
@@ -1393,16 +1471,16 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B7" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C7" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D7">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1411,13 +1489,13 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B8" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C8" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D8">
         <v>175</v>
@@ -1429,13 +1507,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B9" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C9" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D9">
         <v>175</v>
@@ -1447,13 +1525,13 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B10" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C10" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="D10">
         <v>160</v>
@@ -1465,13 +1543,13 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B11" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C11" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="D11">
         <v>180</v>
@@ -1483,13 +1561,13 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C12" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D12">
         <v>180</v>
@@ -1501,13 +1579,13 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C13" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="D13">
         <v>180</v>
@@ -1519,13 +1597,13 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="D14">
         <v>175</v>
@@ -1537,13 +1615,13 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B15" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C15" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="D15">
         <v>210</v>
@@ -1555,13 +1633,13 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B16" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C16" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="D16">
         <v>180</v>
@@ -1573,13 +1651,13 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B17" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C17" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D17">
         <v>210</v>
@@ -1591,13 +1669,13 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B18" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C18" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D18">
         <v>210</v>
@@ -1609,13 +1687,13 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B19" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C19" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="D19">
         <v>160</v>
@@ -1627,13 +1705,13 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B20" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C20" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="D20">
         <v>225</v>
@@ -1645,13 +1723,13 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B21" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C21" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="D21">
         <v>225</v>
@@ -1663,13 +1741,13 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B22" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C22" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D22">
         <v>225</v>
@@ -1681,13 +1759,13 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B23" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C23" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="D23">
         <v>225</v>
@@ -1699,13 +1777,13 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B24" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C24" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="D24">
         <v>225</v>
@@ -1717,13 +1795,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B25" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C25" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="D25">
         <v>225</v>
@@ -1735,13 +1813,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B26" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C26" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="D26">
         <v>215</v>
@@ -1753,13 +1831,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C27" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="D27">
         <v>220</v>
@@ -1771,13 +1849,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B28" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C28" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="D28">
         <v>225</v>
@@ -1789,13 +1867,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B29" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C29" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="D29">
         <v>225</v>
@@ -1807,13 +1885,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B30" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C30" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="D30">
         <v>225</v>
@@ -1825,13 +1903,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B31" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C31" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="D31">
         <v>180</v>
@@ -1843,33 +1921,31 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>300</v>
+      </c>
+      <c r="C32" t="s">
+        <v>301</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G32" t="s">
-        <v>7</v>
-      </c>
-      <c r="H32" t="s">
-        <v>18</v>
-      </c>
+      <c r="J32"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>41</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -1881,18 +1957,18 @@
         <v>7</v>
       </c>
       <c r="H33" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" t="s">
-        <v>202</v>
+        <v>33</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -1904,15 +1980,21 @@
         <v>7</v>
       </c>
       <c r="H34" t="s">
-        <v>292</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="C35" t="s">
+        <v>195</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -1924,15 +2006,18 @@
         <v>7</v>
       </c>
       <c r="H35" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>42</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -1944,18 +2029,18 @@
         <v>7</v>
       </c>
       <c r="H36" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
-      </c>
-      <c r="C37" t="s">
-        <v>203</v>
+        <v>43</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -1967,21 +2052,21 @@
         <v>7</v>
       </c>
       <c r="H37" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C38" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D38">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -1991,37 +2076,35 @@
       </c>
       <c r="G38" t="s">
         <v>7</v>
+      </c>
+      <c r="H38" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+      <c r="C39" t="s">
+        <v>197</v>
+      </c>
+      <c r="D39">
+        <v>240</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
-      <c r="F39" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G39" t="s">
-        <v>7</v>
-      </c>
-      <c r="H39" t="s">
-        <v>34</v>
-      </c>
+      <c r="F39" s="1"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
-      </c>
-      <c r="D40">
-        <v>210</v>
+        <v>46</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -2031,40 +2114,32 @@
       </c>
       <c r="G40" t="s">
         <v>7</v>
+      </c>
+      <c r="H40" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>47</v>
+      </c>
+      <c r="D41">
+        <v>210</v>
       </c>
       <c r="E41">
         <v>1</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G41" t="s">
-        <v>7</v>
-      </c>
-      <c r="H41" t="s">
-        <v>34</v>
-      </c>
+      <c r="F41" s="1"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
-      </c>
-      <c r="C42" t="s">
-        <v>205</v>
-      </c>
-      <c r="D42">
-        <v>250</v>
+        <v>48</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -2074,34 +2149,35 @@
       </c>
       <c r="G42" t="s">
         <v>7</v>
+      </c>
+      <c r="H42" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>49</v>
+      </c>
+      <c r="C43" t="s">
+        <v>198</v>
+      </c>
+      <c r="D43">
+        <v>250</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G43" t="s">
-        <v>7</v>
-      </c>
-      <c r="H43" t="s">
-        <v>18</v>
-      </c>
+      <c r="F43" s="1"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -2113,79 +2189,68 @@
         <v>7</v>
       </c>
       <c r="H44" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B45" t="s">
-        <v>244</v>
-      </c>
-      <c r="C45" t="s">
-        <v>245</v>
-      </c>
-      <c r="D45">
-        <v>250</v>
+        <v>51</v>
       </c>
       <c r="E45">
         <v>1</v>
       </c>
-      <c r="F45" s="1"/>
+      <c r="F45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G45" t="s">
+        <v>7</v>
+      </c>
+      <c r="H45" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B46" t="s">
-        <v>55</v>
+        <v>237</v>
+      </c>
+      <c r="C46" t="s">
+        <v>238</v>
       </c>
       <c r="D46">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="E46">
         <v>1</v>
       </c>
-      <c r="F46" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G46" t="s">
-        <v>7</v>
-      </c>
+      <c r="F46" s="1"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>52</v>
+      </c>
+      <c r="D47">
+        <v>230</v>
       </c>
       <c r="E47">
         <v>1</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G47" t="s">
-        <v>7</v>
-      </c>
-      <c r="H47" t="s">
-        <v>35</v>
-      </c>
+      <c r="F47" s="1"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
-      </c>
-      <c r="C48" t="s">
-        <v>206</v>
-      </c>
-      <c r="D48">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -2197,54 +2262,59 @@
         <v>7</v>
       </c>
       <c r="H48" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B49" t="s">
-        <v>37</v>
+        <v>54</v>
+      </c>
+      <c r="C49" t="s">
+        <v>199</v>
       </c>
       <c r="D49">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="E49">
         <v>1</v>
       </c>
-      <c r="F49" s="1"/>
+      <c r="F49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G49" t="s">
+        <v>7</v>
+      </c>
+      <c r="H49" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
-      </c>
-      <c r="C50" t="s">
-        <v>207</v>
+        <v>34</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="E50">
         <v>1</v>
       </c>
       <c r="F50" s="1"/>
-      <c r="G50" t="s">
-        <v>7</v>
-      </c>
-      <c r="H50" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B51" t="s">
-        <v>59</v>
+        <v>55</v>
+      </c>
+      <c r="C51" t="s">
+        <v>200</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2252,20 +2322,22 @@
       <c r="E51">
         <v>1</v>
       </c>
-      <c r="F51" s="1"/>
+      <c r="F51" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="G51" t="s">
         <v>7</v>
       </c>
       <c r="H51" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="B52" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2277,18 +2349,18 @@
         <v>6</v>
       </c>
       <c r="G52" t="s">
-        <v>167</v>
+        <v>7</v>
       </c>
       <c r="H52" t="s">
-        <v>171</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B53" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2300,18 +2372,18 @@
         <v>6</v>
       </c>
       <c r="G53" t="s">
-        <v>7</v>
+        <v>161</v>
       </c>
       <c r="H53" t="s">
-        <v>23</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B54" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2326,33 +2398,38 @@
         <v>7</v>
       </c>
       <c r="H54" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B55" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D55">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E55">
         <v>1</v>
       </c>
-      <c r="F55" s="1"/>
+      <c r="F55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G55" t="s">
+        <v>7</v>
+      </c>
+      <c r="H55" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B56" t="s">
-        <v>84</v>
-      </c>
-      <c r="C56" t="s">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2367,18 +2444,18 @@
         <v>7</v>
       </c>
       <c r="H56" t="s">
-        <v>25</v>
+        <v>297</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B57" t="s">
-        <v>209</v>
+        <v>81</v>
       </c>
       <c r="C57" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2393,18 +2470,18 @@
         <v>7</v>
       </c>
       <c r="H57" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B58" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C58" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2419,305 +2496,293 @@
         <v>7</v>
       </c>
       <c r="H58" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B59" t="s">
-        <v>85</v>
+        <v>203</v>
+      </c>
+      <c r="C59" t="s">
+        <v>203</v>
       </c>
       <c r="D59">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="E59">
         <v>1</v>
       </c>
-      <c r="F59" s="1"/>
+      <c r="F59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G59" t="s">
+        <v>7</v>
+      </c>
+      <c r="H59" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B60" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="D60">
+        <v>140</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+      <c r="F60" s="1"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>158</v>
+      </c>
+      <c r="B61" t="s">
+        <v>110</v>
+      </c>
+      <c r="D61">
         <v>45</v>
       </c>
-      <c r="E60">
-        <v>1</v>
-      </c>
-      <c r="F60" s="1"/>
-    </row>
-    <row r="61" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A61" t="s">
-        <v>164</v>
-      </c>
-      <c r="B61" t="s">
-        <v>117</v>
-      </c>
-      <c r="D61">
-        <v>0</v>
-      </c>
       <c r="E61">
         <v>1</v>
       </c>
-      <c r="F61" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="H61" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="F61" s="1"/>
+    </row>
+    <row r="62" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B62" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D62">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="E62">
         <v>1</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H62">
-        <v>60</v>
+        <v>273</v>
+      </c>
+      <c r="H62" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B63" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D63">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E63">
         <v>1</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H63">
-        <v>60</v>
+        <v>290</v>
+      </c>
+      <c r="H63" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B64" t="s">
+        <v>113</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="H64" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A65" t="s">
+        <v>158</v>
+      </c>
+      <c r="B65" t="s">
+        <v>114</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="H65" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A66" t="s">
+        <v>158</v>
+      </c>
+      <c r="B66" t="s">
+        <v>115</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="H66" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A67" t="s">
+        <v>158</v>
+      </c>
+      <c r="B67" t="s">
+        <v>116</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="H67" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A68" t="s">
+        <v>158</v>
+      </c>
+      <c r="B68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="H68" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A69" t="s">
+        <v>158</v>
+      </c>
+      <c r="B69" t="s">
+        <v>289</v>
+      </c>
+      <c r="D69">
+        <v>48</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A70" t="s">
+        <v>158</v>
+      </c>
+      <c r="B70" t="s">
+        <v>118</v>
+      </c>
+      <c r="D70">
+        <v>65</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+      <c r="F70" s="1"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A71" t="s">
+        <v>158</v>
+      </c>
+      <c r="B71" t="s">
+        <v>119</v>
+      </c>
+      <c r="D71">
+        <v>70</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+      <c r="F71" s="1"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A72" t="s">
+        <v>158</v>
+      </c>
+      <c r="B72" t="s">
+        <v>307</v>
+      </c>
+      <c r="D72">
+        <v>60</v>
+      </c>
+      <c r="E72">
+        <v>1</v>
+      </c>
+      <c r="F72" s="1"/>
+    </row>
+    <row r="73" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A73" t="s">
+        <v>158</v>
+      </c>
+      <c r="B73" t="s">
         <v>120</v>
-      </c>
-      <c r="D64">
-        <v>50</v>
-      </c>
-      <c r="E64">
-        <v>1</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H64">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A65" t="s">
-        <v>164</v>
-      </c>
-      <c r="B65" t="s">
-        <v>121</v>
-      </c>
-      <c r="D65">
-        <v>65</v>
-      </c>
-      <c r="E65">
-        <v>1</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H65">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A66" t="s">
-        <v>164</v>
-      </c>
-      <c r="B66" t="s">
-        <v>122</v>
-      </c>
-      <c r="D66">
-        <v>50</v>
-      </c>
-      <c r="E66">
-        <v>1</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H66">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A67" t="s">
-        <v>164</v>
-      </c>
-      <c r="B67" t="s">
-        <v>123</v>
-      </c>
-      <c r="D67">
-        <v>65</v>
-      </c>
-      <c r="E67">
-        <v>1</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H67">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A68" t="s">
-        <v>164</v>
-      </c>
-      <c r="B68" t="s">
-        <v>124</v>
-      </c>
-      <c r="D68">
-        <v>65</v>
-      </c>
-      <c r="E68">
-        <v>1</v>
-      </c>
-      <c r="F68" s="1"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A69" t="s">
-        <v>164</v>
-      </c>
-      <c r="B69" t="s">
-        <v>125</v>
-      </c>
-      <c r="D69">
-        <v>70</v>
-      </c>
-      <c r="E69">
-        <v>1</v>
-      </c>
-      <c r="F69" s="1"/>
-    </row>
-    <row r="70" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A70" t="s">
-        <v>164</v>
-      </c>
-      <c r="B70" t="s">
-        <v>126</v>
-      </c>
-      <c r="D70">
-        <v>85</v>
-      </c>
-      <c r="E70">
-        <v>1</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H70">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A71" t="s">
-        <v>164</v>
-      </c>
-      <c r="B71" t="s">
-        <v>127</v>
-      </c>
-      <c r="D71">
-        <v>85</v>
-      </c>
-      <c r="E71">
-        <v>1</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H71">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A72" t="s">
-        <v>164</v>
-      </c>
-      <c r="B72" t="s">
-        <v>128</v>
-      </c>
-      <c r="D72">
-        <v>85</v>
-      </c>
-      <c r="E72">
-        <v>1</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H72">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A73" t="s">
-        <v>164</v>
-      </c>
-      <c r="B73" t="s">
-        <v>129</v>
       </c>
       <c r="D73">
         <v>85</v>
@@ -2726,1134 +2791,1061 @@
         <v>1</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H73">
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B74" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D74">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E74">
         <v>1</v>
       </c>
-      <c r="F74" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>22</v>
+      <c r="F74" t="s">
+        <v>6</v>
+      </c>
+      <c r="G74" t="s">
+        <v>315</v>
       </c>
       <c r="H74">
+        <v>10</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K74">
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B75" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D75">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E75">
         <v>1</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H75">
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B76" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D76">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E76">
         <v>1</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H76">
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B77" t="s">
-        <v>133</v>
+        <v>296</v>
       </c>
       <c r="D77">
+        <v>85</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A78" t="s">
+        <v>158</v>
+      </c>
+      <c r="B78" t="s">
+        <v>124</v>
+      </c>
+      <c r="D78">
+        <v>88</v>
+      </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H78">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A79" t="s">
+        <v>158</v>
+      </c>
+      <c r="B79" t="s">
+        <v>125</v>
+      </c>
+      <c r="D79">
+        <v>88</v>
+      </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H79">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A80" t="s">
+        <v>158</v>
+      </c>
+      <c r="B80" t="s">
+        <v>126</v>
+      </c>
+      <c r="D80">
+        <v>88</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A81" t="s">
+        <v>158</v>
+      </c>
+      <c r="B81" t="s">
+        <v>309</v>
+      </c>
+      <c r="D81">
+        <v>70</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+    </row>
+    <row r="82" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A82" t="s">
+        <v>158</v>
+      </c>
+      <c r="B82" t="s">
+        <v>313</v>
+      </c>
+      <c r="D82">
+        <v>68</v>
+      </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H82">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A83" t="s">
+        <v>158</v>
+      </c>
+      <c r="B83" t="s">
+        <v>127</v>
+      </c>
+      <c r="D83">
         <v>65</v>
       </c>
-      <c r="E77">
-        <v>1</v>
-      </c>
-      <c r="F77" s="1"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A78" t="s">
-        <v>164</v>
-      </c>
-      <c r="B78" t="s">
-        <v>134</v>
-      </c>
-      <c r="D78">
+      <c r="E83">
+        <v>1</v>
+      </c>
+      <c r="F83" s="1"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A84" t="s">
+        <v>158</v>
+      </c>
+      <c r="B84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D84">
         <v>85</v>
       </c>
-      <c r="E78">
-        <v>1</v>
-      </c>
-      <c r="F78" s="1"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A79" t="s">
-        <v>164</v>
-      </c>
-      <c r="B79" t="s">
+      <c r="E84">
+        <v>1</v>
+      </c>
+      <c r="F84" s="1"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A85" t="s">
+        <v>158</v>
+      </c>
+      <c r="B85" t="s">
+        <v>129</v>
+      </c>
+      <c r="D85">
+        <v>95</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="F85" s="1"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A86" t="s">
+        <v>158</v>
+      </c>
+      <c r="B86" t="s">
+        <v>130</v>
+      </c>
+      <c r="D86">
+        <v>45</v>
+      </c>
+      <c r="E86">
+        <v>1</v>
+      </c>
+      <c r="F86" s="1"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A87" t="s">
+        <v>158</v>
+      </c>
+      <c r="B87" t="s">
+        <v>131</v>
+      </c>
+      <c r="D87">
+        <v>150</v>
+      </c>
+      <c r="E87">
+        <v>1</v>
+      </c>
+      <c r="F87" s="1"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A88" t="s">
+        <v>158</v>
+      </c>
+      <c r="B88" t="s">
+        <v>275</v>
+      </c>
+      <c r="D88">
+        <v>65</v>
+      </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
+      <c r="F88" s="1"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A89" t="s">
+        <v>158</v>
+      </c>
+      <c r="B89" t="s">
+        <v>287</v>
+      </c>
+      <c r="D89">
+        <v>25</v>
+      </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
+      <c r="F89" s="1"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A90" t="s">
+        <v>158</v>
+      </c>
+      <c r="B90" t="s">
+        <v>306</v>
+      </c>
+      <c r="D90">
         <v>135</v>
       </c>
-      <c r="D79">
-        <v>95</v>
-      </c>
-      <c r="E79">
-        <v>1</v>
-      </c>
-      <c r="F79" s="1"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A80" t="s">
-        <v>164</v>
-      </c>
-      <c r="B80" t="s">
-        <v>136</v>
-      </c>
-      <c r="D80">
-        <v>45</v>
-      </c>
-      <c r="E80">
-        <v>1</v>
-      </c>
-      <c r="F80" s="1"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A81" t="s">
-        <v>164</v>
-      </c>
-      <c r="B81" t="s">
-        <v>137</v>
-      </c>
-      <c r="D81">
+      <c r="E90">
+        <v>1</v>
+      </c>
+      <c r="F90" s="1"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A91" t="s">
+        <v>158</v>
+      </c>
+      <c r="B91" t="s">
+        <v>308</v>
+      </c>
+      <c r="D91">
+        <v>90</v>
+      </c>
+      <c r="E91">
+        <v>1</v>
+      </c>
+      <c r="F91" s="1"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A92" t="s">
+        <v>158</v>
+      </c>
+      <c r="B92" t="s">
+        <v>310</v>
+      </c>
+      <c r="D92">
+        <v>25</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+      <c r="F92" s="1"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A93" t="s">
+        <v>158</v>
+      </c>
+      <c r="B93" t="s">
+        <v>311</v>
+      </c>
+      <c r="D93">
+        <v>88</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+      <c r="F93" s="1"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A94" t="s">
+        <v>158</v>
+      </c>
+      <c r="B94" t="s">
+        <v>312</v>
+      </c>
+      <c r="D94">
+        <v>350</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+      <c r="F94" s="1"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A95" t="s">
+        <v>158</v>
+      </c>
+      <c r="B95" t="s">
+        <v>316</v>
+      </c>
+      <c r="D95">
+        <v>120</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+      <c r="F95" s="1"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A96" t="s">
+        <v>158</v>
+      </c>
+      <c r="B96" t="s">
+        <v>317</v>
+      </c>
+      <c r="D96">
+        <v>48</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+      <c r="F96" s="1"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A97" t="s">
+        <v>158</v>
+      </c>
+      <c r="B97" t="s">
+        <v>318</v>
+      </c>
+      <c r="D97">
         <v>150</v>
       </c>
-      <c r="E81">
-        <v>1</v>
-      </c>
-      <c r="F81" s="1"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A82" t="s">
-        <v>164</v>
-      </c>
-      <c r="B82" t="s">
-        <v>282</v>
-      </c>
-      <c r="D82">
-        <v>65</v>
-      </c>
-      <c r="E82">
-        <v>1</v>
-      </c>
-      <c r="F82" s="1"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A83" t="s">
-        <v>164</v>
-      </c>
-      <c r="B83" t="s">
-        <v>283</v>
-      </c>
-      <c r="D83">
+      <c r="E97">
+        <v>1</v>
+      </c>
+      <c r="F97" s="1"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A98" t="s">
+        <v>146</v>
+      </c>
+      <c r="B98" t="s">
+        <v>139</v>
+      </c>
+      <c r="D98">
+        <v>285</v>
+      </c>
+      <c r="E98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A99" t="s">
+        <v>146</v>
+      </c>
+      <c r="B99" t="s">
+        <v>140</v>
+      </c>
+      <c r="D99">
+        <v>325</v>
+      </c>
+      <c r="E99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A100" t="s">
+        <v>146</v>
+      </c>
+      <c r="B100" t="s">
+        <v>141</v>
+      </c>
+      <c r="D100">
+        <v>325</v>
+      </c>
+      <c r="E100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A101" t="s">
+        <v>146</v>
+      </c>
+      <c r="B101" t="s">
+        <v>142</v>
+      </c>
+      <c r="D101">
+        <v>335</v>
+      </c>
+      <c r="E101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A102" t="s">
+        <v>146</v>
+      </c>
+      <c r="B102" t="s">
+        <v>143</v>
+      </c>
+      <c r="D102">
+        <v>340</v>
+      </c>
+      <c r="E102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A103" t="s">
+        <v>146</v>
+      </c>
+      <c r="B103" t="s">
+        <v>144</v>
+      </c>
+      <c r="D103">
+        <v>350</v>
+      </c>
+      <c r="E103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A104" t="s">
+        <v>145</v>
+      </c>
+      <c r="B104" t="s">
+        <v>37</v>
+      </c>
+      <c r="C104" t="s">
+        <v>204</v>
+      </c>
+      <c r="D104">
+        <v>260</v>
+      </c>
+      <c r="E104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
+        <v>145</v>
+      </c>
+      <c r="B105" t="s">
+        <v>38</v>
+      </c>
+      <c r="C105" t="s">
+        <v>205</v>
+      </c>
+      <c r="D105">
+        <v>330</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>145</v>
+      </c>
+      <c r="B106" t="s">
+        <v>33</v>
+      </c>
+      <c r="D106">
+        <v>230</v>
+      </c>
+      <c r="E106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A107" t="s">
+        <v>145</v>
+      </c>
+      <c r="B107" t="s">
+        <v>39</v>
+      </c>
+      <c r="C107" t="s">
+        <v>206</v>
+      </c>
+      <c r="D107">
+        <v>240</v>
+      </c>
+      <c r="E107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A108" t="s">
+        <v>145</v>
+      </c>
+      <c r="B108" t="s">
+        <v>40</v>
+      </c>
+      <c r="C108" t="s">
+        <v>195</v>
+      </c>
+      <c r="D108">
+        <v>220</v>
+      </c>
+      <c r="E108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
+        <v>145</v>
+      </c>
+      <c r="B109" t="s">
+        <v>239</v>
+      </c>
+      <c r="D109">
+        <v>260</v>
+      </c>
+      <c r="E109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A110" t="s">
+        <v>145</v>
+      </c>
+      <c r="B110" t="s">
+        <v>34</v>
+      </c>
+      <c r="D110">
+        <v>310</v>
+      </c>
+      <c r="E110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A111" t="s">
+        <v>145</v>
+      </c>
+      <c r="B111" t="s">
+        <v>35</v>
+      </c>
+      <c r="D111">
+        <v>280</v>
+      </c>
+      <c r="E111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A112" t="s">
+        <v>145</v>
+      </c>
+      <c r="B112" t="s">
+        <v>36</v>
+      </c>
+      <c r="D112">
+        <v>245</v>
+      </c>
+      <c r="E112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A113" t="s">
+        <v>153</v>
+      </c>
+      <c r="B113" t="s">
+        <v>83</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="E113">
+        <v>1</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G113" t="s">
+        <v>7</v>
+      </c>
+      <c r="H113" t="s">
+        <v>24</v>
+      </c>
+      <c r="J113"/>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A114" t="s">
+        <v>153</v>
+      </c>
+      <c r="B114" t="s">
+        <v>84</v>
+      </c>
+      <c r="C114" t="s">
+        <v>207</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114">
+        <v>1</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G114" t="s">
+        <v>7</v>
+      </c>
+      <c r="H114" t="s">
         <v>25</v>
       </c>
-      <c r="E83">
-        <v>1</v>
-      </c>
-      <c r="F83" s="1"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A84" t="s">
-        <v>152</v>
-      </c>
-      <c r="B84" t="s">
-        <v>145</v>
-      </c>
-      <c r="D84">
+      <c r="J114"/>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A115" t="s">
+        <v>153</v>
+      </c>
+      <c r="B115" t="s">
+        <v>85</v>
+      </c>
+      <c r="C115" t="s">
+        <v>208</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <v>1</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G115" t="s">
+        <v>7</v>
+      </c>
+      <c r="H115" t="s">
+        <v>25</v>
+      </c>
+      <c r="J115"/>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A116" t="s">
+        <v>153</v>
+      </c>
+      <c r="B116" t="s">
+        <v>86</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>1</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G116" t="s">
+        <v>7</v>
+      </c>
+      <c r="H116" t="s">
+        <v>25</v>
+      </c>
+      <c r="J116"/>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A117" t="s">
+        <v>153</v>
+      </c>
+      <c r="B117" t="s">
+        <v>212</v>
+      </c>
+      <c r="C117" t="s">
+        <v>213</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <v>1</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G117" t="s">
+        <v>7</v>
+      </c>
+      <c r="H117" t="s">
+        <v>25</v>
+      </c>
+      <c r="J117"/>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A118" t="s">
+        <v>153</v>
+      </c>
+      <c r="B118" t="s">
+        <v>298</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>1</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G118" t="s">
+        <v>7</v>
+      </c>
+      <c r="H118" t="s">
+        <v>25</v>
+      </c>
+      <c r="J118"/>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A119" t="s">
+        <v>153</v>
+      </c>
+      <c r="B119" t="s">
+        <v>87</v>
+      </c>
+      <c r="C119" t="s">
+        <v>209</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119">
+        <v>1</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G119" t="s">
+        <v>161</v>
+      </c>
+      <c r="H119" t="s">
+        <v>162</v>
+      </c>
+      <c r="J119"/>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A120" t="s">
+        <v>153</v>
+      </c>
+      <c r="B120" t="s">
+        <v>88</v>
+      </c>
+      <c r="C120" t="s">
+        <v>210</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <v>1</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G120" t="s">
+        <v>161</v>
+      </c>
+      <c r="H120" t="s">
+        <v>162</v>
+      </c>
+      <c r="J120"/>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A121" t="s">
+        <v>153</v>
+      </c>
+      <c r="B121" t="s">
+        <v>89</v>
+      </c>
+      <c r="C121" t="s">
+        <v>211</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="E121">
+        <v>1</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G121" t="s">
+        <v>161</v>
+      </c>
+      <c r="H121" t="s">
+        <v>162</v>
+      </c>
+      <c r="J121"/>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A122" t="s">
+        <v>154</v>
+      </c>
+      <c r="B122" t="s">
+        <v>90</v>
+      </c>
+      <c r="C122" t="s">
+        <v>214</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="E122">
+        <v>1</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G122" t="s">
+        <v>7</v>
+      </c>
+      <c r="H122" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A123" t="s">
+        <v>154</v>
+      </c>
+      <c r="B123" t="s">
+        <v>91</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="E123">
+        <v>1</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G123" t="s">
+        <v>7</v>
+      </c>
+      <c r="H123" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A124" t="s">
+        <v>154</v>
+      </c>
+      <c r="B124" t="s">
         <v>285</v>
       </c>
-      <c r="E84">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A85" t="s">
-        <v>152</v>
-      </c>
-      <c r="B85" t="s">
-        <v>146</v>
-      </c>
-      <c r="D85">
-        <v>325</v>
-      </c>
-      <c r="E85">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A86" t="s">
-        <v>152</v>
-      </c>
-      <c r="B86" t="s">
-        <v>147</v>
-      </c>
-      <c r="D86">
-        <v>325</v>
-      </c>
-      <c r="E86">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A87" t="s">
-        <v>152</v>
-      </c>
-      <c r="B87" t="s">
-        <v>148</v>
-      </c>
-      <c r="D87">
-        <v>335</v>
-      </c>
-      <c r="E87">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A88" t="s">
-        <v>152</v>
-      </c>
-      <c r="B88" t="s">
-        <v>149</v>
-      </c>
-      <c r="D88">
-        <v>340</v>
-      </c>
-      <c r="E88">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A89" t="s">
-        <v>152</v>
-      </c>
-      <c r="B89" t="s">
-        <v>150</v>
-      </c>
-      <c r="D89">
-        <v>350</v>
-      </c>
-      <c r="E89">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A90" t="s">
-        <v>151</v>
-      </c>
-      <c r="B90" t="s">
-        <v>40</v>
-      </c>
-      <c r="C90" t="s">
-        <v>211</v>
-      </c>
-      <c r="D90">
-        <v>260</v>
-      </c>
-      <c r="E90">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A91" t="s">
-        <v>151</v>
-      </c>
-      <c r="B91" t="s">
-        <v>41</v>
-      </c>
-      <c r="C91" t="s">
-        <v>212</v>
-      </c>
-      <c r="D91">
-        <v>330</v>
-      </c>
-      <c r="E91">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A92" t="s">
-        <v>151</v>
-      </c>
-      <c r="B92" t="s">
-        <v>36</v>
-      </c>
-      <c r="D92">
-        <v>230</v>
-      </c>
-      <c r="E92">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A93" t="s">
-        <v>151</v>
-      </c>
-      <c r="B93" t="s">
-        <v>42</v>
-      </c>
-      <c r="C93" t="s">
-        <v>213</v>
-      </c>
-      <c r="D93">
+      <c r="C124" t="s">
+        <v>286</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124">
+        <v>1</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G124" t="s">
+        <v>7</v>
+      </c>
+      <c r="H124" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A125" t="s">
+        <v>154</v>
+      </c>
+      <c r="B125" t="s">
+        <v>284</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+      <c r="E125">
+        <v>1</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G125" t="s">
+        <v>7</v>
+      </c>
+      <c r="H125" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A126" t="s">
+        <v>154</v>
+      </c>
+      <c r="B126" t="s">
+        <v>92</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+      <c r="E126">
+        <v>1</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G126" t="s">
+        <v>7</v>
+      </c>
+      <c r="H126" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A127" t="s">
+        <v>154</v>
+      </c>
+      <c r="B127" t="s">
         <v>240</v>
       </c>
-      <c r="E93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A94" t="s">
-        <v>151</v>
-      </c>
-      <c r="B94" t="s">
-        <v>43</v>
-      </c>
-      <c r="C94" t="s">
-        <v>202</v>
-      </c>
-      <c r="D94">
-        <v>220</v>
-      </c>
-      <c r="E94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A95" t="s">
-        <v>151</v>
-      </c>
-      <c r="B95" t="s">
-        <v>246</v>
-      </c>
-      <c r="D95">
-        <v>260</v>
-      </c>
-      <c r="E95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A96" t="s">
-        <v>151</v>
-      </c>
-      <c r="B96" t="s">
-        <v>37</v>
-      </c>
-      <c r="D96">
-        <v>310</v>
-      </c>
-      <c r="E96">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A97" t="s">
-        <v>151</v>
-      </c>
-      <c r="B97" t="s">
-        <v>38</v>
-      </c>
-      <c r="D97">
-        <v>280</v>
-      </c>
-      <c r="E97">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A98" t="s">
-        <v>151</v>
-      </c>
-      <c r="B98" t="s">
-        <v>39</v>
-      </c>
-      <c r="D98">
-        <v>245</v>
-      </c>
-      <c r="E98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A99" t="s">
-        <v>159</v>
-      </c>
-      <c r="B99" t="s">
-        <v>86</v>
-      </c>
-      <c r="D99">
-        <v>0</v>
-      </c>
-      <c r="E99">
-        <v>1</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G99" t="s">
-        <v>7</v>
-      </c>
-      <c r="H99" t="s">
-        <v>27</v>
-      </c>
-      <c r="J99"/>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A100" t="s">
-        <v>159</v>
-      </c>
-      <c r="B100" t="s">
-        <v>87</v>
-      </c>
-      <c r="C100" t="s">
-        <v>214</v>
-      </c>
-      <c r="D100">
-        <v>0</v>
-      </c>
-      <c r="E100">
-        <v>1</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G100" t="s">
-        <v>7</v>
-      </c>
-      <c r="H100" t="s">
-        <v>28</v>
-      </c>
-      <c r="J100"/>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A101" t="s">
-        <v>159</v>
-      </c>
-      <c r="B101" t="s">
-        <v>88</v>
-      </c>
-      <c r="C101" t="s">
-        <v>215</v>
-      </c>
-      <c r="D101">
-        <v>0</v>
-      </c>
-      <c r="E101">
-        <v>1</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G101" t="s">
-        <v>7</v>
-      </c>
-      <c r="H101" t="s">
-        <v>28</v>
-      </c>
-      <c r="J101"/>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A102" t="s">
-        <v>159</v>
-      </c>
-      <c r="B102" t="s">
-        <v>89</v>
-      </c>
-      <c r="D102">
-        <v>0</v>
-      </c>
-      <c r="E102">
-        <v>1</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G102" t="s">
-        <v>7</v>
-      </c>
-      <c r="H102" t="s">
-        <v>28</v>
-      </c>
-      <c r="J102"/>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A103" t="s">
-        <v>159</v>
-      </c>
-      <c r="B103" t="s">
-        <v>219</v>
-      </c>
-      <c r="C103" t="s">
-        <v>220</v>
-      </c>
-      <c r="D103">
-        <v>0</v>
-      </c>
-      <c r="E103">
-        <v>1</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G103" t="s">
-        <v>7</v>
-      </c>
-      <c r="H103" t="s">
-        <v>28</v>
-      </c>
-      <c r="J103"/>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A104" t="s">
-        <v>159</v>
-      </c>
-      <c r="B104" t="s">
-        <v>90</v>
-      </c>
-      <c r="D104">
-        <v>0</v>
-      </c>
-      <c r="E104">
-        <v>1</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G104" t="s">
-        <v>7</v>
-      </c>
-      <c r="H104" t="s">
-        <v>28</v>
-      </c>
-      <c r="J104"/>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A105" t="s">
-        <v>159</v>
-      </c>
-      <c r="B105" t="s">
-        <v>91</v>
-      </c>
-      <c r="C105" t="s">
-        <v>216</v>
-      </c>
-      <c r="D105">
-        <v>0</v>
-      </c>
-      <c r="E105">
-        <v>1</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G105" t="s">
-        <v>167</v>
-      </c>
-      <c r="H105" t="s">
-        <v>169</v>
-      </c>
-      <c r="J105"/>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A106" t="s">
-        <v>159</v>
-      </c>
-      <c r="B106" t="s">
-        <v>92</v>
-      </c>
-      <c r="C106" t="s">
-        <v>217</v>
-      </c>
-      <c r="D106">
-        <v>0</v>
-      </c>
-      <c r="E106">
-        <v>1</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G106" t="s">
-        <v>167</v>
-      </c>
-      <c r="H106" t="s">
-        <v>169</v>
-      </c>
-      <c r="J106"/>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A107" t="s">
-        <v>159</v>
-      </c>
-      <c r="B107" t="s">
+      <c r="C127" t="s">
+        <v>241</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+      <c r="E127">
+        <v>1</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G127" t="s">
+        <v>7</v>
+      </c>
+      <c r="H127" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A128" t="s">
+        <v>154</v>
+      </c>
+      <c r="B128" t="s">
         <v>93</v>
       </c>
-      <c r="C107" t="s">
-        <v>218</v>
-      </c>
-      <c r="D107">
-        <v>0</v>
-      </c>
-      <c r="E107">
-        <v>1</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G107" t="s">
-        <v>167</v>
-      </c>
-      <c r="H107" t="s">
-        <v>169</v>
-      </c>
-      <c r="J107"/>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A108" t="s">
-        <v>160</v>
-      </c>
-      <c r="B108" t="s">
-        <v>94</v>
-      </c>
-      <c r="C108" t="s">
-        <v>221</v>
-      </c>
-      <c r="D108">
-        <v>0</v>
-      </c>
-      <c r="E108">
-        <v>1</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G108" t="s">
-        <v>7</v>
-      </c>
-      <c r="H108" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A109" t="s">
-        <v>160</v>
-      </c>
-      <c r="B109" t="s">
-        <v>95</v>
-      </c>
-      <c r="D109">
-        <v>0</v>
-      </c>
-      <c r="E109">
-        <v>1</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G109" t="s">
-        <v>7</v>
-      </c>
-      <c r="H109" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A110" t="s">
-        <v>160</v>
-      </c>
-      <c r="B110" t="s">
-        <v>96</v>
-      </c>
-      <c r="D110">
-        <v>0</v>
-      </c>
-      <c r="E110">
-        <v>1</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G110" t="s">
-        <v>7</v>
-      </c>
-      <c r="H110" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A111" t="s">
-        <v>160</v>
-      </c>
-      <c r="B111" t="s">
-        <v>97</v>
-      </c>
-      <c r="D111">
-        <v>0</v>
-      </c>
-      <c r="E111">
-        <v>1</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G111" t="s">
-        <v>7</v>
-      </c>
-      <c r="H111" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A112" t="s">
-        <v>160</v>
-      </c>
-      <c r="B112" t="s">
-        <v>247</v>
-      </c>
-      <c r="C112" t="s">
-        <v>248</v>
-      </c>
-      <c r="D112">
-        <v>0</v>
-      </c>
-      <c r="E112">
-        <v>1</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G112" t="s">
-        <v>7</v>
-      </c>
-      <c r="H112" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A113" t="s">
-        <v>160</v>
-      </c>
-      <c r="B113" t="s">
-        <v>98</v>
-      </c>
-      <c r="D113">
-        <v>0</v>
-      </c>
-      <c r="E113">
-        <v>1</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G113" t="s">
-        <v>7</v>
-      </c>
-      <c r="H113" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A114" t="s">
-        <v>156</v>
-      </c>
-      <c r="B114" t="s">
-        <v>65</v>
-      </c>
-      <c r="D114">
-        <v>0</v>
-      </c>
-      <c r="E114">
-        <v>1</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G114" t="s">
-        <v>7</v>
-      </c>
-      <c r="H114" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A115" t="s">
-        <v>156</v>
-      </c>
-      <c r="B115" t="s">
-        <v>66</v>
-      </c>
-      <c r="D115">
-        <v>0</v>
-      </c>
-      <c r="E115">
-        <v>1</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G115" t="s">
-        <v>7</v>
-      </c>
-      <c r="H115" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A116" t="s">
-        <v>156</v>
-      </c>
-      <c r="B116" t="s">
-        <v>67</v>
-      </c>
-      <c r="C116" t="s">
-        <v>222</v>
-      </c>
-      <c r="D116">
-        <v>0</v>
-      </c>
-      <c r="E116">
-        <v>1</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G116" t="s">
-        <v>7</v>
-      </c>
-      <c r="H116" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A117" t="s">
-        <v>156</v>
-      </c>
-      <c r="B117" t="s">
-        <v>68</v>
-      </c>
-      <c r="C117" t="s">
-        <v>223</v>
-      </c>
-      <c r="D117">
-        <v>0</v>
-      </c>
-      <c r="E117">
-        <v>1</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G117" t="s">
-        <v>7</v>
-      </c>
-      <c r="H117" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A118" t="s">
-        <v>156</v>
-      </c>
-      <c r="B118" t="s">
-        <v>69</v>
-      </c>
-      <c r="C118" t="s">
-        <v>224</v>
-      </c>
-      <c r="D118">
-        <v>0</v>
-      </c>
-      <c r="E118">
-        <v>1</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G118" t="s">
-        <v>7</v>
-      </c>
-      <c r="H118" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A119" t="s">
-        <v>156</v>
-      </c>
-      <c r="B119" t="s">
-        <v>70</v>
-      </c>
-      <c r="C119" t="s">
-        <v>225</v>
-      </c>
-      <c r="D119">
-        <v>0</v>
-      </c>
-      <c r="E119">
-        <v>1</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G119" t="s">
-        <v>7</v>
-      </c>
-      <c r="H119" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A120" t="s">
-        <v>156</v>
-      </c>
-      <c r="B120" t="s">
-        <v>71</v>
-      </c>
-      <c r="C120" t="s">
-        <v>226</v>
-      </c>
-      <c r="D120">
-        <v>0</v>
-      </c>
-      <c r="E120">
-        <v>1</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G120" t="s">
-        <v>7</v>
-      </c>
-      <c r="H120" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A121" t="s">
-        <v>156</v>
-      </c>
-      <c r="B121" t="s">
-        <v>72</v>
-      </c>
-      <c r="D121">
-        <v>0</v>
-      </c>
-      <c r="E121">
-        <v>1</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G121" t="s">
-        <v>167</v>
-      </c>
-      <c r="H121" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A122" t="s">
-        <v>156</v>
-      </c>
-      <c r="B122" t="s">
-        <v>170</v>
-      </c>
-      <c r="D122">
-        <v>50</v>
-      </c>
-      <c r="E122">
-        <v>1</v>
-      </c>
-      <c r="F122" s="1"/>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A123" t="s">
-        <v>157</v>
-      </c>
-      <c r="B123" t="s">
-        <v>39</v>
-      </c>
-      <c r="D123">
-        <v>0</v>
-      </c>
-      <c r="E123">
-        <v>1</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G123" t="s">
-        <v>7</v>
-      </c>
-      <c r="H123" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A124" t="s">
-        <v>157</v>
-      </c>
-      <c r="B124" t="s">
-        <v>73</v>
-      </c>
-      <c r="C124" t="s">
-        <v>227</v>
-      </c>
-      <c r="D124">
-        <v>0</v>
-      </c>
-      <c r="E124">
-        <v>1</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G124" t="s">
-        <v>7</v>
-      </c>
-      <c r="H124" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A125" t="s">
-        <v>157</v>
-      </c>
-      <c r="B125" t="s">
-        <v>74</v>
-      </c>
-      <c r="C125" t="s">
-        <v>228</v>
-      </c>
-      <c r="D125">
-        <v>0</v>
-      </c>
-      <c r="E125">
-        <v>1</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G125" t="s">
-        <v>7</v>
-      </c>
-      <c r="H125" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A126" t="s">
-        <v>157</v>
-      </c>
-      <c r="B126" t="s">
-        <v>75</v>
-      </c>
-      <c r="C126" t="s">
-        <v>229</v>
-      </c>
-      <c r="D126">
-        <v>0</v>
-      </c>
-      <c r="E126">
-        <v>1</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G126" t="s">
-        <v>7</v>
-      </c>
-      <c r="H126" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A127" t="s">
-        <v>157</v>
-      </c>
-      <c r="B127" t="s">
-        <v>76</v>
-      </c>
-      <c r="C127" t="s">
-        <v>230</v>
-      </c>
-      <c r="D127">
-        <v>250</v>
-      </c>
-      <c r="E127">
-        <v>1</v>
-      </c>
-      <c r="F127" s="1"/>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A128" t="s">
-        <v>157</v>
-      </c>
-      <c r="B128" t="s">
-        <v>77</v>
-      </c>
-      <c r="C128" t="s">
-        <v>231</v>
-      </c>
       <c r="D128">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E128">
         <v>1</v>
@@ -3862,16 +3854,13 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B129" t="s">
-        <v>78</v>
-      </c>
-      <c r="C129" t="s">
-        <v>232</v>
+        <v>314</v>
       </c>
       <c r="D129">
-        <v>230</v>
+        <v>310</v>
       </c>
       <c r="E129">
         <v>1</v>
@@ -3880,25 +3869,33 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="B130" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="D130">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E130">
         <v>1</v>
       </c>
-      <c r="F130" s="1"/>
+      <c r="F130" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G130" t="s">
+        <v>7</v>
+      </c>
+      <c r="H130" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="B131" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -3913,18 +3910,18 @@
         <v>7</v>
       </c>
       <c r="H131" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="B132" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="C132" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -3939,15 +3936,18 @@
         <v>7</v>
       </c>
       <c r="H132" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="B133" t="s">
-        <v>101</v>
+        <v>65</v>
+      </c>
+      <c r="C133" t="s">
+        <v>216</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -3962,18 +3962,18 @@
         <v>7</v>
       </c>
       <c r="H133" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="B134" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="C134" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -3988,18 +3988,18 @@
         <v>7</v>
       </c>
       <c r="H134" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="B135" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="C135" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -4014,18 +4014,18 @@
         <v>7</v>
       </c>
       <c r="H135" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="B136" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="C136" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -4040,480 +4040,892 @@
         <v>7</v>
       </c>
       <c r="H136" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
+        <v>150</v>
+      </c>
+      <c r="B137" t="s">
+        <v>69</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+      <c r="E137">
+        <v>1</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G137" t="s">
         <v>161</v>
       </c>
-      <c r="B137" t="s">
-        <v>105</v>
-      </c>
-      <c r="D137">
-        <v>0</v>
-      </c>
-      <c r="E137">
-        <v>1</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G137" t="s">
-        <v>7</v>
-      </c>
       <c r="H137" t="s">
-        <v>17</v>
+        <v>302</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B138" t="s">
-        <v>106</v>
+        <v>163</v>
       </c>
       <c r="D138">
-        <v>295</v>
+        <v>50</v>
       </c>
       <c r="E138">
         <v>1</v>
       </c>
+      <c r="F138" s="1"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="B139" t="s">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="D139">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="E139">
         <v>1</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G139" t="s">
+        <v>7</v>
+      </c>
+      <c r="H139" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="B140" t="s">
-        <v>108</v>
+        <v>70</v>
+      </c>
+      <c r="C140" t="s">
+        <v>220</v>
       </c>
       <c r="D140">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="E140">
         <v>1</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G140" t="s">
+        <v>7</v>
+      </c>
+      <c r="H140" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="B141" t="s">
-        <v>109</v>
+        <v>71</v>
+      </c>
+      <c r="C141" t="s">
+        <v>221</v>
       </c>
       <c r="D141">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="E141">
         <v>1</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G141" t="s">
+        <v>7</v>
+      </c>
+      <c r="H141" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="B142" t="s">
-        <v>110</v>
+        <v>72</v>
+      </c>
+      <c r="C142" t="s">
+        <v>222</v>
       </c>
       <c r="D142">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="E142">
         <v>1</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G142" t="s">
+        <v>7</v>
+      </c>
+      <c r="H142" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B143" t="s">
-        <v>111</v>
+        <v>73</v>
+      </c>
+      <c r="C143" t="s">
+        <v>223</v>
       </c>
       <c r="D143">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="E143">
         <v>1</v>
       </c>
+      <c r="F143" s="1"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B144" t="s">
-        <v>112</v>
+        <v>74</v>
+      </c>
+      <c r="C144" t="s">
+        <v>224</v>
       </c>
       <c r="D144">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="E144">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="F144" s="1"/>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B145" t="s">
-        <v>113</v>
+        <v>75</v>
+      </c>
+      <c r="C145" t="s">
+        <v>225</v>
       </c>
       <c r="D145">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="E145">
         <v>1</v>
       </c>
-    </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="F145" s="1"/>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="D146">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="E146">
         <v>1</v>
       </c>
-    </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="F146" s="1"/>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B147" t="s">
-        <v>115</v>
+        <v>283</v>
       </c>
       <c r="D147">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="E147">
         <v>1</v>
       </c>
-    </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="F147" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G147" t="s">
+        <v>7</v>
+      </c>
+      <c r="H147" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
         <v>155</v>
       </c>
       <c r="B148" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="D148">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="E148">
         <v>1</v>
       </c>
-    </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="F148" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G148" t="s">
+        <v>7</v>
+      </c>
+      <c r="H148" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
         <v>155</v>
       </c>
       <c r="B149" t="s">
-        <v>61</v>
+        <v>95</v>
+      </c>
+      <c r="C149" t="s">
+        <v>226</v>
       </c>
       <c r="D149">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="E149">
         <v>1</v>
       </c>
-    </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="F149" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G149" t="s">
+        <v>7</v>
+      </c>
+      <c r="H149" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="D150">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="E150">
         <v>1</v>
       </c>
-    </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="F150" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G150" t="s">
+        <v>7</v>
+      </c>
+      <c r="H150" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
         <v>155</v>
       </c>
       <c r="B151" t="s">
-        <v>38</v>
+        <v>97</v>
+      </c>
+      <c r="C151" t="s">
+        <v>227</v>
       </c>
       <c r="D151">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="E151">
         <v>1</v>
       </c>
-    </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="F151" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G151" t="s">
+        <v>7</v>
+      </c>
+      <c r="H151" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
         <v>155</v>
       </c>
       <c r="B152" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="C152" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="D152">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="E152">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="F152" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G152" t="s">
+        <v>7</v>
+      </c>
+      <c r="H152" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
         <v>155</v>
       </c>
       <c r="B153" t="s">
-        <v>64</v>
+        <v>99</v>
+      </c>
+      <c r="C153" t="s">
+        <v>229</v>
       </c>
       <c r="D153">
+        <v>0</v>
+      </c>
+      <c r="E153">
+        <v>1</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G153" t="s">
+        <v>7</v>
+      </c>
+      <c r="H153" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A154" t="s">
+        <v>155</v>
+      </c>
+      <c r="B154" t="s">
+        <v>100</v>
+      </c>
+      <c r="D154">
+        <v>0</v>
+      </c>
+      <c r="E154">
+        <v>1</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G154" t="s">
+        <v>7</v>
+      </c>
+      <c r="H154" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A155" t="s">
+        <v>156</v>
+      </c>
+      <c r="B155" t="s">
+        <v>101</v>
+      </c>
+      <c r="D155">
+        <v>295</v>
+      </c>
+      <c r="E155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A156" t="s">
+        <v>156</v>
+      </c>
+      <c r="B156" t="s">
+        <v>102</v>
+      </c>
+      <c r="D156">
+        <v>295</v>
+      </c>
+      <c r="E156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A157" t="s">
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
+        <v>303</v>
+      </c>
+      <c r="D157">
+        <v>295</v>
+      </c>
+      <c r="E157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A158" t="s">
+        <v>156</v>
+      </c>
+      <c r="B158" t="s">
+        <v>103</v>
+      </c>
+      <c r="D158">
+        <v>295</v>
+      </c>
+      <c r="E158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A159" t="s">
+        <v>156</v>
+      </c>
+      <c r="B159" t="s">
+        <v>104</v>
+      </c>
+      <c r="D159">
+        <v>245</v>
+      </c>
+      <c r="E159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A160" t="s">
+        <v>156</v>
+      </c>
+      <c r="B160" t="s">
+        <v>105</v>
+      </c>
+      <c r="D160">
+        <v>295</v>
+      </c>
+      <c r="E160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A161" t="s">
+        <v>157</v>
+      </c>
+      <c r="B161" t="s">
+        <v>106</v>
+      </c>
+      <c r="D161">
+        <v>240</v>
+      </c>
+      <c r="E161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A162" t="s">
+        <v>157</v>
+      </c>
+      <c r="B162" t="s">
+        <v>107</v>
+      </c>
+      <c r="D162">
+        <v>290</v>
+      </c>
+      <c r="E162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A163" t="s">
+        <v>157</v>
+      </c>
+      <c r="B163" t="s">
+        <v>108</v>
+      </c>
+      <c r="D163">
+        <v>290</v>
+      </c>
+      <c r="E163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A164" t="s">
+        <v>157</v>
+      </c>
+      <c r="B164" t="s">
+        <v>109</v>
+      </c>
+      <c r="D164">
+        <v>240</v>
+      </c>
+      <c r="E164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A165" t="s">
+        <v>157</v>
+      </c>
+      <c r="B165" t="s">
+        <v>304</v>
+      </c>
+      <c r="D165">
+        <v>240</v>
+      </c>
+      <c r="E165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A166" t="s">
+        <v>157</v>
+      </c>
+      <c r="B166" t="s">
+        <v>288</v>
+      </c>
+      <c r="C166" t="s">
+        <v>288</v>
+      </c>
+      <c r="D166">
+        <v>240</v>
+      </c>
+      <c r="E166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A167" t="s">
+        <v>149</v>
+      </c>
+      <c r="B167" t="s">
+        <v>57</v>
+      </c>
+      <c r="D167">
+        <v>350</v>
+      </c>
+      <c r="E167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A168" t="s">
+        <v>149</v>
+      </c>
+      <c r="B168" t="s">
+        <v>58</v>
+      </c>
+      <c r="D168">
+        <v>350</v>
+      </c>
+      <c r="E168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A169" t="s">
+        <v>149</v>
+      </c>
+      <c r="B169" t="s">
+        <v>59</v>
+      </c>
+      <c r="D169">
+        <v>370</v>
+      </c>
+      <c r="E169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A170" t="s">
+        <v>149</v>
+      </c>
+      <c r="B170" t="s">
         <v>35</v>
       </c>
-      <c r="E153">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A154" t="s">
-        <v>166</v>
-      </c>
-      <c r="B154" t="s">
-        <v>143</v>
-      </c>
-      <c r="C154" t="s">
-        <v>238</v>
-      </c>
-      <c r="D154">
+      <c r="D170">
+        <v>280</v>
+      </c>
+      <c r="E170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A171" t="s">
+        <v>149</v>
+      </c>
+      <c r="B171" t="s">
+        <v>60</v>
+      </c>
+      <c r="C171" t="s">
+        <v>230</v>
+      </c>
+      <c r="D171">
+        <v>350</v>
+      </c>
+      <c r="E171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A172" t="s">
+        <v>149</v>
+      </c>
+      <c r="B172" t="s">
+        <v>61</v>
+      </c>
+      <c r="D172">
+        <v>35</v>
+      </c>
+      <c r="E172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A173" t="s">
+        <v>160</v>
+      </c>
+      <c r="B173" t="s">
+        <v>137</v>
+      </c>
+      <c r="C173" t="s">
+        <v>231</v>
+      </c>
+      <c r="D173">
         <v>100</v>
       </c>
-      <c r="E154">
-        <v>1</v>
-      </c>
-      <c r="P154" s="1"/>
-    </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A155" t="s">
-        <v>166</v>
-      </c>
-      <c r="B155" t="s">
-        <v>138</v>
-      </c>
-      <c r="C155" t="s">
-        <v>239</v>
-      </c>
-      <c r="D155">
+      <c r="E173">
+        <v>1</v>
+      </c>
+      <c r="P173" s="1"/>
+    </row>
+    <row r="174" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A174" t="s">
+        <v>160</v>
+      </c>
+      <c r="B174" t="s">
+        <v>132</v>
+      </c>
+      <c r="C174" t="s">
+        <v>232</v>
+      </c>
+      <c r="D174">
         <v>100</v>
       </c>
-      <c r="E155">
-        <v>1</v>
-      </c>
-      <c r="P155" s="1"/>
-    </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A156" t="s">
-        <v>166</v>
-      </c>
-      <c r="B156" t="s">
-        <v>139</v>
-      </c>
-      <c r="C156" t="s">
-        <v>240</v>
-      </c>
-      <c r="D156">
+      <c r="E174">
+        <v>1</v>
+      </c>
+      <c r="P174" s="1"/>
+    </row>
+    <row r="175" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A175" t="s">
+        <v>160</v>
+      </c>
+      <c r="B175" t="s">
+        <v>133</v>
+      </c>
+      <c r="C175" t="s">
+        <v>233</v>
+      </c>
+      <c r="D175">
         <v>130</v>
       </c>
-      <c r="E156">
-        <v>1</v>
-      </c>
-      <c r="P156" s="1"/>
-    </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A157" t="s">
-        <v>166</v>
-      </c>
-      <c r="B157" t="s">
-        <v>140</v>
-      </c>
-      <c r="C157" t="s">
-        <v>85</v>
-      </c>
-      <c r="D157">
+      <c r="E175">
+        <v>1</v>
+      </c>
+      <c r="P175" s="1"/>
+    </row>
+    <row r="176" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A176" t="s">
+        <v>160</v>
+      </c>
+      <c r="B176" t="s">
+        <v>134</v>
+      </c>
+      <c r="C176" t="s">
+        <v>82</v>
+      </c>
+      <c r="D176">
         <v>130</v>
       </c>
-      <c r="E157">
-        <v>1</v>
-      </c>
-      <c r="P157" s="1"/>
-    </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A158" t="s">
-        <v>166</v>
-      </c>
-      <c r="B158" t="s">
-        <v>141</v>
-      </c>
-      <c r="D158">
+      <c r="E176">
+        <v>1</v>
+      </c>
+      <c r="P176" s="1"/>
+    </row>
+    <row r="177" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A177" t="s">
+        <v>160</v>
+      </c>
+      <c r="B177" t="s">
+        <v>135</v>
+      </c>
+      <c r="D177">
         <v>55</v>
       </c>
-      <c r="E158">
-        <v>1</v>
-      </c>
-      <c r="P158" s="1"/>
-    </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A159" t="s">
-        <v>166</v>
-      </c>
-      <c r="B159" t="s">
-        <v>142</v>
-      </c>
-      <c r="D159">
+      <c r="E177">
+        <v>1</v>
+      </c>
+      <c r="P177" s="1"/>
+    </row>
+    <row r="178" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A178" t="s">
+        <v>160</v>
+      </c>
+      <c r="B178" t="s">
+        <v>136</v>
+      </c>
+      <c r="D178">
         <v>25</v>
       </c>
-      <c r="E159">
-        <v>1</v>
-      </c>
-      <c r="P159" s="1"/>
-    </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A160" t="s">
-        <v>158</v>
-      </c>
-      <c r="B160" t="s">
-        <v>285</v>
-      </c>
-      <c r="D160">
-        <v>0</v>
-      </c>
-      <c r="E160">
-        <v>1</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G160" t="s">
-        <v>167</v>
-      </c>
-      <c r="H160" t="s">
-        <v>284</v>
-      </c>
-      <c r="P160" t="str">
-        <f xml:space="preserve"> PROPER(R160)</f>
+      <c r="E178">
+        <v>1</v>
+      </c>
+      <c r="P178" s="1"/>
+    </row>
+    <row r="179" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A179" t="s">
+        <v>152</v>
+      </c>
+      <c r="B179" t="s">
+        <v>277</v>
+      </c>
+      <c r="D179">
+        <v>0</v>
+      </c>
+      <c r="E179">
+        <v>1</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G179" t="s">
+        <v>161</v>
+      </c>
+      <c r="H179" t="s">
+        <v>276</v>
+      </c>
+      <c r="P179" t="str">
+        <f xml:space="preserve"> PROPER(R179)</f>
         <v/>
       </c>
-      <c r="T160" s="1"/>
-    </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A161" t="s">
-        <v>158</v>
-      </c>
-      <c r="B161" t="s">
-        <v>289</v>
-      </c>
-      <c r="D161">
+      <c r="T179" s="1"/>
+    </row>
+    <row r="180" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A180" t="s">
+        <v>152</v>
+      </c>
+      <c r="B180" t="s">
+        <v>280</v>
+      </c>
+      <c r="D180">
         <v>200</v>
       </c>
-      <c r="E161">
-        <v>1</v>
-      </c>
-      <c r="P161" t="str">
-        <f xml:space="preserve"> PROPER(R161)</f>
+      <c r="E180">
+        <v>1</v>
+      </c>
+      <c r="P180" t="str">
+        <f xml:space="preserve"> PROPER(R180)</f>
         <v/>
       </c>
-      <c r="T161" s="1"/>
-    </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A162" t="s">
-        <v>158</v>
-      </c>
-      <c r="B162" t="s">
-        <v>288</v>
-      </c>
-      <c r="D162">
+      <c r="T180" s="1"/>
+    </row>
+    <row r="181" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A181" t="s">
+        <v>152</v>
+      </c>
+      <c r="B181" t="s">
+        <v>299</v>
+      </c>
+      <c r="D181">
         <v>55</v>
       </c>
-      <c r="E162">
-        <v>1</v>
-      </c>
-      <c r="P162" t="str">
-        <f xml:space="preserve"> PROPER(R162)</f>
+      <c r="E181">
+        <v>1</v>
+      </c>
+      <c r="P181" t="str">
+        <f xml:space="preserve"> PROPER(R181)</f>
         <v/>
       </c>
-      <c r="T162" s="1"/>
-    </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A163" t="s">
-        <v>158</v>
-      </c>
-      <c r="B163" t="s">
-        <v>286</v>
-      </c>
-      <c r="D163">
+      <c r="T181" s="1"/>
+    </row>
+    <row r="182" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A182" t="s">
+        <v>152</v>
+      </c>
+      <c r="B182" t="s">
+        <v>278</v>
+      </c>
+      <c r="D182">
         <v>80</v>
       </c>
-      <c r="E163">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A164" t="s">
-        <v>158</v>
-      </c>
-      <c r="B164" t="s">
-        <v>287</v>
-      </c>
-      <c r="D164">
+      <c r="E182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A183" t="s">
+        <v>152</v>
+      </c>
+      <c r="B183" t="s">
+        <v>279</v>
+      </c>
+      <c r="D183">
         <v>120</v>
       </c>
-      <c r="E164">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A165" t="s">
-        <v>158</v>
-      </c>
-      <c r="B165" t="s">
-        <v>290</v>
-      </c>
-      <c r="D165">
+      <c r="E183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A184" t="s">
+        <v>152</v>
+      </c>
+      <c r="B184" t="s">
+        <v>281</v>
+      </c>
+      <c r="D184">
         <v>50</v>
       </c>
-      <c r="E165">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A166" t="s">
-        <v>158</v>
-      </c>
-      <c r="B166" t="s">
-        <v>291</v>
-      </c>
-      <c r="D166">
+      <c r="E184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A185" t="s">
+        <v>152</v>
+      </c>
+      <c r="B185" t="s">
+        <v>282</v>
+      </c>
+      <c r="D185">
         <v>180</v>
       </c>
-      <c r="E166">
+      <c r="E185">
         <v>1</v>
       </c>
     </row>
